--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>239.119</t>
+          <t>181.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>99.96</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>102.99</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.47</t>
+          <t>103.51</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.79</t>
+          <t>-119.38</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34409216.48986976</t>
+          <t>34398913.20086706</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>33418956.2</t>
+          <t>35759848.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>21669007.2</t>
+          <t>22584742.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>19787904.64</t>
+          <t>19380974.5</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>11749949</t>
+          <t>13175105</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1258656.897391115</t>
+          <t>1411158.904500055</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>3191815.58</v>
+        <v>2249919.94</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,77 +1177,77 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-5.180998587442668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-18.45076376795075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-4.337749221712871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>32.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>15.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1262,32 +1262,32 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>211.11</t>
+          <t>239.119</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>48.60</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.96</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.99</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.43</t>
+          <t>103.47</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-124.87</t>
+          <t>-121.79</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34409216.48986976</t>
+          <t>34398913.20086706</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>21554889.0</t>
+          <t>24164678.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30017543.0</t>
+          <t>33418956.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20200254.1</t>
+          <t>21669007.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>20264334.1</t>
+          <t>19787904.64</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>9817288</t>
+          <t>11749949</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>907173.5011915436</t>
+          <t>1258656.897391115</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>3782839.03</v>
+        <v>3191815.58</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,77 +1608,77 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-5.180998587442668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-18.45076376795075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-4.337749221712871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>32.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>15.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1693,32 +1693,32 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>470.424</t>
+          <t>211.11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.80</t>
+          <t>48.60</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>100.56</t>
+          <t>100.88</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>99.84</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>103.46</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.43</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-128.50</t>
+          <t>-124.87</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34409216.48986976</t>
+          <t>34398913.20086706</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>48495487.0</t>
+          <t>21554889.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>27651156.2</t>
+          <t>30017543.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>20066315.5</t>
+          <t>20200254.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>20877613.24</t>
+          <t>20264334.1</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>7584840</t>
+          <t>9817288</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>384325.22296158</t>
+          <t>907173.5011915436</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>4771677.11</v>
+        <v>3782839.03</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,77 +2039,77 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-5.180998587442668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-18.45076376795075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-4.337749221712871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>32.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>15.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2134,22 +2134,22 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>651.618</t>
+          <t>470.424</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>37.80</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.84</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.46</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.34</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-132.10</t>
+          <t>-128.50</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34409216.48986976</t>
+          <t>34398913.20086706</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>66397962.0</t>
+          <t>48495487.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>20992977.0</t>
+          <t>27651156.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16244706.1</t>
+          <t>20066315.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>20629028.38</t>
+          <t>20877613.24</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>4748270</t>
+          <t>7584840</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-413375.1199286837</t>
+          <t>384325.22296158</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>3127393.25</v>
+        <v>4771677.11</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,77 +2470,77 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-5.180998587442668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-18.45076376795075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-4.337749221712871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>32.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>15.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2555,32 +2555,32 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>65.452</t>
+          <t>651.618</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>99.02000000000001</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>99.61</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>103.89</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-134.44</t>
+          <t>-132.10</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34409216.48986976</t>
+          <t>34398913.20086706</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6481765.0</t>
+          <t>66397962.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>9409637.2</t>
+          <t>20992977.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>11476200.4</t>
+          <t>16244706.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>21347947.28</t>
+          <t>20629028.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2066563</t>
+          <t>4748270</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1057151.187417239</t>
+          <t>-413375.1199286837</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-1251398.63</v>
+        <v>3127393.25</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,27 +2901,27 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-5.180998587442668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-18.45076376795075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-4.337749221712871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,47 +2931,47 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>32.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>15.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,32 +2986,32 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71.787</t>
+          <t>65.452</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-20.96</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.04</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>99.14</t>
+          <t>99.02000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>99.61</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>104.14</t>
+          <t>103.89</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.27</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-135.72</t>
+          <t>-134.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34409216.48986976</t>
+          <t>34398913.20086706</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7157612.0</t>
+          <t>6481765.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>9919058.2</t>
+          <t>9409637.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12549366.3</t>
+          <t>11476200.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>21865999.16</t>
+          <t>21347947.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2630308</t>
+          <t>-2066563</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1021833.471363163</t>
+          <t>-1057151.187417239</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1042530.25</v>
+        <v>-1251398.63</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-9.64</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-5.180998587442668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-18.45076376795075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-4.337749221712871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,47 +3362,47 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>32.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>15.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3417,32 +3417,32 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>97.646</t>
+          <t>71.787</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-20.96</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.59</t>
+          <t>-12.04</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>99.14</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>99.92</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>104.36</t>
+          <t>104.14</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>103.27</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>11.87</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-137.02</t>
+          <t>-135.72</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34409216.48986976</t>
+          <t>34398913.20086706</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>9722955.0</t>
+          <t>7157612.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>10382965.2</t>
+          <t>9919058.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13126733.5</t>
+          <t>12549366.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>22279772.86</t>
+          <t>21865999.16</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2743768</t>
+          <t>-2630308</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1018070.420875835</t>
+          <t>-1021833.471363163</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-779325.8100000001</v>
+        <v>-1042530.25</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-9.18</t>
+          <t>-9.64</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,27 +3763,27 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-5.180998587442668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-18.45076376795075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-4.337749221712871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,47 +3793,47 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>32.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>15.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>155.305</t>
+          <t>97.646</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-20.90</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.10</t>
+          <t>-11.59</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>99.92</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>104.57</t>
+          <t>104.36</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.21</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>11.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.12</t>
+          <t>-137.02</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34409216.48986976</t>
+          <t>34398913.20086706</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15204591.0</t>
+          <t>9722955.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>12481474.8</t>
+          <t>10382965.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12896327.1</t>
+          <t>13126733.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>22808200.88</t>
+          <t>22279772.86</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-414852</t>
+          <t>-2743768</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1061478.532091404</t>
+          <t>-1018070.420875835</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-650344.58</v>
+        <v>-779325.8100000001</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-9.18</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,77 +4194,77 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-5.180998587442668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-18.45076376795075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-4.337749221712871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>32.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>15.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>97.2</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>85.527</t>
+          <t>155.305</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-13.10</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>99.32</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>100.18</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>104.82</t>
+          <t>104.57</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.23</t>
+          <t>103.21</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.59</t>
+          <t>-138.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34409216.48986976</t>
+          <t>34398913.20086706</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8481263.0</t>
+          <t>15204591.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>11496435.2</t>
+          <t>12481474.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12242942.4</t>
+          <t>12896327.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>23555516.64</t>
+          <t>22808200.88</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-746507</t>
+          <t>-414852</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1136230.159653444</t>
+          <t>-1061478.532091404</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1030177.23</v>
+        <v>-650344.58</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,77 +4625,77 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-5.180998587442668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-18.45076376795075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-4.337749221712871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>32.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>15.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4710,32 +4710,32 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>90.975</t>
+          <t>85.527</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,57 +4888,57 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>99.3</t>
+          <t>99.32</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>100.33</t>
+          <t>100.18</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>105.03</t>
+          <t>104.82</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -4948,17 +4948,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-139.32</t>
+          <t>-138.59</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34409216.48986976</t>
+          <t>34398913.20086706</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9028870.0</t>
+          <t>8481263.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>13542763.6</t>
+          <t>11496435.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>11865800.3</t>
+          <t>12242942.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>24317372.14</t>
+          <t>23555516.64</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1676963</t>
+          <t>-746507</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1155512.509941705</t>
+          <t>-1136230.159653444</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-815646.6899999999</v>
+        <v>-1030177.23</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-5.180998587442668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-18.45076376795075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-4.337749221712871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,47 +5086,47 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>32.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>15.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,32 +5141,32 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>99.7</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>99.8</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>95.27</t>
+          <t>90.975</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.30</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>48.33</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>99.28</t>
+          <t>99.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>100.48</t>
+          <t>100.33</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>105.26</t>
+          <t>105.03</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.22</t>
+          <t>103.23</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-140.27</t>
+          <t>-139.32</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34409216.48986976</t>
+          <t>34398913.20086706</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9477147.0</t>
+          <t>9028870.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>15179674.4</t>
+          <t>13542763.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11598407.6</t>
+          <t>11865800.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24964693.12</t>
+          <t>24317372.14</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3581266</t>
+          <t>1676963</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1217306.294895072</t>
+          <t>-1155512.509941705</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-538716.4300000001</v>
+        <v>-815646.6899999999</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-5.180998587442668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-18.45076376795075</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-4.337749221712871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,47 +5517,47 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>32.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>15.64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>181.83</t>
+          <t>202.457</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.83</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.51</t>
+          <t>103.52</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-119.38</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34398913.20086706</t>
+          <t>34392565.63636363</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>35759848.6</t>
+          <t>26480263.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>22584742.9</t>
+          <t>23736620.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>19380974.5</t>
+          <t>19242893.34</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>13175105</t>
+          <t>2743643</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1411158.904500055</t>
+          <t>1451039.154113366</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>2249919.94</v>
+        <v>1670380.53</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,27 +1177,27 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.7848146795386409</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.78483981056313</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.753976956109076</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,47 +1207,47 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.64%</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.64%</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1262,32 +1262,32 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>239.119</t>
+          <t>181.83</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>99.96</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>102.99</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.47</t>
+          <t>103.51</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-121.79</t>
+          <t>-119.38</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34398913.20086706</t>
+          <t>34392565.63636363</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>33418956.2</t>
+          <t>35759848.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>21669007.2</t>
+          <t>22584742.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>19787904.64</t>
+          <t>19380974.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>11749949</t>
+          <t>13175105</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1258656.897391115</t>
+          <t>1411158.904500055</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>3191815.58</v>
+        <v>2249919.94</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,77 +1608,77 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.7848146795386409</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.78483981056313</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.753976956109076</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.64%</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.64%</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1693,32 +1693,32 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>211.11</t>
+          <t>239.119</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>48.60</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.96</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.99</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.43</t>
+          <t>103.47</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-124.87</t>
+          <t>-121.79</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34398913.20086706</t>
+          <t>34392565.63636363</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>21554889.0</t>
+          <t>24164678.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30017543.0</t>
+          <t>33418956.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>20200254.1</t>
+          <t>21669007.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>20264334.1</t>
+          <t>19787904.64</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>9817288</t>
+          <t>11749949</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>907173.5011915436</t>
+          <t>1258656.897391115</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>3782839.03</v>
+        <v>3191815.58</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,77 +2039,77 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.7848146795386409</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.78483981056313</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.753976956109076</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.64%</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.64%</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>470.424</t>
+          <t>211.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.80</t>
+          <t>48.60</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,245 +2302,245 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-3.17</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>100.88</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>99.93</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>103.43</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>58.34</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-124.87</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>34392565.63636363</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>21554889.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>30017543.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>20200254.1</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>20264334.1</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>9817288</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>907173.5011915436</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>3782839.03</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-7.73</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>100.56</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>99.84</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>103.46</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>103.4</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>50.58</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-128.50</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>34398913.20086706</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>48495487.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>27651156.2</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>20066315.5</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>20877613.24</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>7584840</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>384325.22296158</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>4771677.11</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-6.36</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.7848146795386409</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.78483981056313</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.753976956109076</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.64%</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.64%</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2565,22 +2565,22 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>651.618</t>
+          <t>470.424</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>37.80</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.84</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.34</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-132.10</t>
+          <t>-128.50</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34398913.20086706</t>
+          <t>34392565.63636363</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>66397962.0</t>
+          <t>48495487.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>20992977.0</t>
+          <t>27651156.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16244706.1</t>
+          <t>20066315.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>20629028.38</t>
+          <t>20877613.24</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4748270</t>
+          <t>7584840</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-413375.1199286837</t>
+          <t>384325.22296158</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>3127393.25</v>
+        <v>4771677.11</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,77 +2901,77 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.7848146795386409</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.78483981056313</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.753976956109076</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.64%</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.64%</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,32 +2986,32 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>65.452</t>
+          <t>651.618</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>32.37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>99.02000000000001</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>99.61</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>103.89</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-134.44</t>
+          <t>-132.10</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34398913.20086706</t>
+          <t>34392565.63636363</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6481765.0</t>
+          <t>66397962.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>9409637.2</t>
+          <t>20992977.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>11476200.4</t>
+          <t>16244706.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>21347947.28</t>
+          <t>20629028.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2066563</t>
+          <t>4748270</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1057151.187417239</t>
+          <t>-413375.1199286837</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1251398.63</v>
+        <v>3127393.25</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,77 +3332,77 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.7848146795386409</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.78483981056313</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.753976956109076</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.64%</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.64%</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3417,32 +3417,32 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>71.787</t>
+          <t>65.452</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-20.96</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.04</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>99.14</t>
+          <t>99.02000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>99.61</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>104.14</t>
+          <t>103.89</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.27</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-135.72</t>
+          <t>-134.44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34398913.20086706</t>
+          <t>34392565.63636363</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>7157612.0</t>
+          <t>6481765.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>9919058.2</t>
+          <t>9409637.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12549366.3</t>
+          <t>11476200.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>21865999.16</t>
+          <t>21347947.28</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2630308</t>
+          <t>-2066563</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1021833.471363163</t>
+          <t>-1057151.187417239</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1042530.25</v>
+        <v>-1251398.63</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-9.64</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,27 +3763,27 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.7848146795386409</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.78483981056313</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.753976956109076</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,47 +3793,47 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.64%</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.64%</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3848,32 +3848,32 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>97.646</t>
+          <t>71.787</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-20.96</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.59</t>
+          <t>-12.04</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>99.14</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>99.92</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>104.36</t>
+          <t>104.14</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>103.27</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>11.87</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-137.02</t>
+          <t>-135.72</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34398913.20086706</t>
+          <t>34392565.63636363</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9722955.0</t>
+          <t>7157612.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>10382965.2</t>
+          <t>9919058.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13126733.5</t>
+          <t>12549366.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>22279772.86</t>
+          <t>21865999.16</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2743768</t>
+          <t>-2630308</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1018070.420875835</t>
+          <t>-1021833.471363163</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-779325.8100000001</v>
+        <v>-1042530.25</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-9.18</t>
+          <t>-9.64</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,27 +4194,27 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.7848146795386409</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.78483981056313</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.753976956109076</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,47 +4224,47 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.64%</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.64%</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4289,22 +4289,22 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>155.305</t>
+          <t>97.646</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-20.90</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.10</t>
+          <t>-11.59</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>99.92</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>104.57</t>
+          <t>104.36</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.21</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>11.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.12</t>
+          <t>-137.02</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34398913.20086706</t>
+          <t>34392565.63636363</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15204591.0</t>
+          <t>9722955.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>12481474.8</t>
+          <t>10382965.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12896327.1</t>
+          <t>13126733.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>22808200.88</t>
+          <t>22279772.86</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-414852</t>
+          <t>-2743768</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1061478.532091404</t>
+          <t>-1018070.420875835</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-650344.58</v>
+        <v>-779325.8100000001</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-9.18</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,77 +4625,77 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.7848146795386409</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.78483981056313</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.753976956109076</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.64%</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.64%</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4710,32 +4710,32 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>97.2</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>85.527</t>
+          <t>155.305</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-13.10</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>99.32</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>100.18</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>104.82</t>
+          <t>104.57</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.23</t>
+          <t>103.21</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.59</t>
+          <t>-138.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34398913.20086706</t>
+          <t>34392565.63636363</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8481263.0</t>
+          <t>15204591.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>11496435.2</t>
+          <t>12481474.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12242942.4</t>
+          <t>12896327.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>23555516.64</t>
+          <t>22808200.88</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-746507</t>
+          <t>-414852</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1136230.159653444</t>
+          <t>-1061478.532091404</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1030177.23</v>
+        <v>-650344.58</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.7848146795386409</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.78483981056313</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.753976956109076</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,47 +5086,47 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.64%</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.64%</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,32 +5141,32 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>90.975</t>
+          <t>85.527</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,57 +5319,57 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>99.3</t>
+          <t>99.32</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>100.33</t>
+          <t>100.18</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>105.03</t>
+          <t>104.82</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5379,17 +5379,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-139.32</t>
+          <t>-138.59</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34398913.20086706</t>
+          <t>34392565.63636363</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9028870.0</t>
+          <t>8481263.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>13542763.6</t>
+          <t>11496435.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11865800.3</t>
+          <t>12242942.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24317372.14</t>
+          <t>23555516.64</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1676963</t>
+          <t>-746507</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1155512.509941705</t>
+          <t>-1136230.159653444</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-815646.6899999999</v>
+        <v>-1030177.23</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.7848146795386409</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28.78483981056313</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7.753976956109076</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,47 +5517,47 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.64%</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.64%</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>99.7</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
           <t>99.8</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>202.457</t>
+          <t>90.678</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>-19.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>99.82000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>99.83</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.18</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.52</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-117.55</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34392565.63636363</t>
+          <t>34362335.48559078</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>26480263.0</t>
+          <t>18569544.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>23736620.0</t>
+          <t>23110350.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>19242893.34</t>
+          <t>18738868.34</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2743643</t>
+          <t>-4540805</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1451039.154113366</t>
+          <t>1288353.579970241</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1670380.53</v>
+        <v>393582.92</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>181.83</t>
+          <t>202.457</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.83</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.51</t>
+          <t>103.52</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-119.38</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34392565.63636363</t>
+          <t>34362335.48559078</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>35759848.6</t>
+          <t>26480263.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>22584742.9</t>
+          <t>23736620.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>19380974.5</t>
+          <t>19242893.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>13175105</t>
+          <t>2743643</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1411158.904500055</t>
+          <t>1451039.154113366</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2249919.94</v>
+        <v>1670380.53</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>239.119</t>
+          <t>181.83</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>99.96</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>102.99</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.47</t>
+          <t>103.51</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-121.79</t>
+          <t>-119.38</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34392565.63636363</t>
+          <t>34362335.48559078</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>33418956.2</t>
+          <t>35759848.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>21669007.2</t>
+          <t>22584742.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>19787904.64</t>
+          <t>19380974.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>11749949</t>
+          <t>13175105</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1258656.897391115</t>
+          <t>1411158.904500055</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>3191815.58</v>
+        <v>2249919.94</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>100.0</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>211.11</t>
+          <t>239.119</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>48.60</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.96</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.99</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.43</t>
+          <t>103.47</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-124.87</t>
+          <t>-121.79</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34392565.63636363</t>
+          <t>34362335.48559078</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>21554889.0</t>
+          <t>24164678.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30017543.0</t>
+          <t>33418956.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20200254.1</t>
+          <t>21669007.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>20264334.1</t>
+          <t>19787904.64</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9817288</t>
+          <t>11749949</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>907173.5011915436</t>
+          <t>1258656.897391115</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>3782839.03</v>
+        <v>3191815.58</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>470.424</t>
+          <t>211.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.80</t>
+          <t>48.60</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,177 +2733,177 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-3.17</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>100.88</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>99.93</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>103.43</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>58.34</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-124.87</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>34362335.48559078</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>21554889.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>30017543.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>20200254.1</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>20264334.1</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>9817288</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>907173.5011915436</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>3782839.03</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-7.73</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>100.56</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>99.84</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>103.46</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>103.4</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>50.58</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-128.50</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>34392565.63636363</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>48495487.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>27651156.2</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>20066315.5</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>20877613.24</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>7584840</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>384325.22296158</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>4771677.11</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-6.36</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
           <t>0.7848146795386409</t>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>651.618</t>
+          <t>470.424</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>37.80</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.84</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.34</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-132.10</t>
+          <t>-128.50</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34392565.63636363</t>
+          <t>34362335.48559078</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>66397962.0</t>
+          <t>48495487.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>20992977.0</t>
+          <t>27651156.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>16244706.1</t>
+          <t>20066315.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>20629028.38</t>
+          <t>20877613.24</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4748270</t>
+          <t>7584840</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-413375.1199286837</t>
+          <t>384325.22296158</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>3127393.25</v>
+        <v>4771677.11</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>101.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>65.452</t>
+          <t>651.618</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>32.37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>99.02000000000001</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>99.61</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>103.89</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.34</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-134.44</t>
+          <t>-132.10</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34392565.63636363</t>
+          <t>34362335.48559078</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6481765.0</t>
+          <t>66397962.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>9409637.2</t>
+          <t>20992977.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>11476200.4</t>
+          <t>16244706.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>21347947.28</t>
+          <t>20629028.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2066563</t>
+          <t>4748270</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1057151.187417239</t>
+          <t>-413375.1199286837</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1251398.63</v>
+        <v>3127393.25</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>71.787</t>
+          <t>65.452</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20.96</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.04</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>99.14</t>
+          <t>99.02000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>99.61</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>104.14</t>
+          <t>103.89</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.27</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-135.72</t>
+          <t>-134.44</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34392565.63636363</t>
+          <t>34362335.48559078</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7157612.0</t>
+          <t>6481765.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>9919058.2</t>
+          <t>9409637.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12549366.3</t>
+          <t>11476200.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>21865999.16</t>
+          <t>21347947.28</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2630308</t>
+          <t>-2066563</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1021833.471363163</t>
+          <t>-1057151.187417239</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1042530.25</v>
+        <v>-1251398.63</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-9.64</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>97.646</t>
+          <t>71.787</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-20.96</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.59</t>
+          <t>-12.04</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>99.14</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>99.92</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>104.36</t>
+          <t>104.14</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>103.27</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>11.87</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-137.02</t>
+          <t>-135.72</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34392565.63636363</t>
+          <t>34362335.48559078</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9722955.0</t>
+          <t>7157612.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>10382965.2</t>
+          <t>9919058.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13126733.5</t>
+          <t>12549366.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>22279772.86</t>
+          <t>21865999.16</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2743768</t>
+          <t>-2630308</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1018070.420875835</t>
+          <t>-1021833.471363163</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-779325.8100000001</v>
+        <v>-1042530.25</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-9.18</t>
+          <t>-9.64</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>155.305</t>
+          <t>97.646</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-20.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.10</t>
+          <t>-11.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>99.92</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>104.57</t>
+          <t>104.36</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.21</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>11.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.12</t>
+          <t>-137.02</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34392565.63636363</t>
+          <t>34362335.48559078</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>15204591.0</t>
+          <t>9722955.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>12481474.8</t>
+          <t>10382965.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12896327.1</t>
+          <t>13126733.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>22808200.88</t>
+          <t>22279772.86</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-414852</t>
+          <t>-2743768</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1061478.532091404</t>
+          <t>-1018070.420875835</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-650344.58</v>
+        <v>-779325.8100000001</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-9.18</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>97.2</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>85.527</t>
+          <t>155.305</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-13.10</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>99.32</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>100.18</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>104.82</t>
+          <t>104.57</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.23</t>
+          <t>103.21</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.59</t>
+          <t>-138.12</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34392565.63636363</t>
+          <t>34362335.48559078</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8481263.0</t>
+          <t>15204591.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>11496435.2</t>
+          <t>12481474.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>12242942.4</t>
+          <t>12896327.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>23555516.64</t>
+          <t>22808200.88</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-746507</t>
+          <t>-414852</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1136230.159653444</t>
+          <t>-1061478.532091404</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1030177.23</v>
+        <v>-650344.58</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>90.678</t>
+          <t>109.187</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.65</t>
+          <t>-29.23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>99.82000000000001</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>99.72</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>102.18</t>
+          <t>101.95</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.55</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34362335.48559078</t>
+          <t>34336416.92374101</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>18569544.4</t>
+          <t>16438424.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>23110350.3</t>
+          <t>23227983.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>18738868.34</t>
+          <t>18265933.7</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4540805</t>
+          <t>-6789559</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1288353.579970241</t>
+          <t>1034266.833169591</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>393582.92</v>
+        <v>-363210.27</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>202.457</t>
+          <t>90.678</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>-19.65</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>99.82000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>99.83</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.18</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.52</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-117.55</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34362335.48559078</t>
+          <t>34336416.92374101</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>26480263.0</t>
+          <t>18569544.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23736620.0</t>
+          <t>23110350.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>19242893.34</t>
+          <t>18738868.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2743643</t>
+          <t>-4540805</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1451039.154113366</t>
+          <t>1288353.579970241</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1670380.53</v>
+        <v>393582.92</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>181.83</t>
+          <t>202.457</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.83</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.51</t>
+          <t>103.52</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-119.38</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34362335.48559078</t>
+          <t>34336416.92374101</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>35759848.6</t>
+          <t>26480263.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>22584742.9</t>
+          <t>23736620.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>19380974.5</t>
+          <t>19242893.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>13175105</t>
+          <t>2743643</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1411158.904500055</t>
+          <t>1451039.154113366</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>2249919.94</v>
+        <v>1670380.53</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>239.119</t>
+          <t>181.83</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>99.96</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>102.99</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.47</t>
+          <t>103.51</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-121.79</t>
+          <t>-119.38</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34362335.48559078</t>
+          <t>34336416.92374101</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33418956.2</t>
+          <t>35759848.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>21669007.2</t>
+          <t>22584742.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>19787904.64</t>
+          <t>19380974.5</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>11749949</t>
+          <t>13175105</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1258656.897391115</t>
+          <t>1411158.904500055</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>3191815.58</v>
+        <v>2249919.94</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>100.0</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>211.11</t>
+          <t>239.119</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>48.60</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.96</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.99</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.43</t>
+          <t>103.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-124.87</t>
+          <t>-121.79</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34362335.48559078</t>
+          <t>34336416.92374101</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>21554889.0</t>
+          <t>24164678.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30017543.0</t>
+          <t>33418956.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20200254.1</t>
+          <t>21669007.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>20264334.1</t>
+          <t>19787904.64</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>9817288</t>
+          <t>11749949</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>907173.5011915436</t>
+          <t>1258656.897391115</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>3782839.03</v>
+        <v>3191815.58</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>470.424</t>
+          <t>211.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.80</t>
+          <t>48.60</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>100.56</t>
+          <t>100.88</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>99.84</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>103.46</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-128.50</t>
+          <t>-124.87</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34362335.48559078</t>
+          <t>34336416.92374101</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>48495487.0</t>
+          <t>21554889.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>27651156.2</t>
+          <t>30017543.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20066315.5</t>
+          <t>20200254.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>20877613.24</t>
+          <t>20264334.1</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7584840</t>
+          <t>9817288</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>384325.22296158</t>
+          <t>907173.5011915436</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>4771677.11</v>
+        <v>3782839.03</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>651.618</t>
+          <t>470.424</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>37.80</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.84</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.34</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-132.10</t>
+          <t>-128.50</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34362335.48559078</t>
+          <t>34336416.92374101</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>66397962.0</t>
+          <t>48495487.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20992977.0</t>
+          <t>27651156.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>16244706.1</t>
+          <t>20066315.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>20629028.38</t>
+          <t>20877613.24</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4748270</t>
+          <t>7584840</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-413375.1199286837</t>
+          <t>384325.22296158</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>3127393.25</v>
+        <v>4771677.11</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>101.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>65.452</t>
+          <t>651.618</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>32.37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>99.02000000000001</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>99.61</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>103.89</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.34</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-134.44</t>
+          <t>-132.10</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34362335.48559078</t>
+          <t>34336416.92374101</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6481765.0</t>
+          <t>66397962.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>9409637.2</t>
+          <t>20992977.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>11476200.4</t>
+          <t>16244706.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>21347947.28</t>
+          <t>20629028.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2066563</t>
+          <t>4748270</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1057151.187417239</t>
+          <t>-413375.1199286837</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1251398.63</v>
+        <v>3127393.25</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>71.787</t>
+          <t>65.452</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.96</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.04</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>99.14</t>
+          <t>99.02000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>99.61</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>104.14</t>
+          <t>103.89</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.27</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-135.72</t>
+          <t>-134.44</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34362335.48559078</t>
+          <t>34336416.92374101</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7157612.0</t>
+          <t>6481765.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>9919058.2</t>
+          <t>9409637.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12549366.3</t>
+          <t>11476200.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>21865999.16</t>
+          <t>21347947.28</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2630308</t>
+          <t>-2066563</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1021833.471363163</t>
+          <t>-1057151.187417239</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1042530.25</v>
+        <v>-1251398.63</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-9.64</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>97.646</t>
+          <t>71.787</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-20.96</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.59</t>
+          <t>-12.04</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>99.14</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>99.92</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>104.36</t>
+          <t>104.14</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>103.27</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>11.87</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-137.02</t>
+          <t>-135.72</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34362335.48559078</t>
+          <t>34336416.92374101</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9722955.0</t>
+          <t>7157612.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>10382965.2</t>
+          <t>9919058.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13126733.5</t>
+          <t>12549366.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>22279772.86</t>
+          <t>21865999.16</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2743768</t>
+          <t>-2630308</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1018070.420875835</t>
+          <t>-1021833.471363163</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-779325.8100000001</v>
+        <v>-1042530.25</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-9.18</t>
+          <t>-9.64</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>155.305</t>
+          <t>97.646</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-20.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.10</t>
+          <t>-11.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.08000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>99.92</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>104.57</t>
+          <t>104.36</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.21</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>11.87</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.12</t>
+          <t>-137.02</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34362335.48559078</t>
+          <t>34336416.92374101</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>15204591.0</t>
+          <t>9722955.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>12481474.8</t>
+          <t>10382965.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>12896327.1</t>
+          <t>13126733.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>22808200.88</t>
+          <t>22279772.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-414852</t>
+          <t>-2743768</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1061478.532091404</t>
+          <t>-1018070.420875835</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-650344.58</v>
+        <v>-779325.8100000001</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-9.18</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>97.2</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>109.187</t>
+          <t>149.664</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-29.23</t>
+          <t>-39.23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,42 +1014,42 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,32 +1059,32 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>99.72</t>
+          <t>99.75</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>101.95</t>
+          <t>101.74</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>103.62</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34336416.92374101</t>
+          <t>34319188.7349138</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>16438424.6</t>
+          <t>14584902.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>23227983.8</t>
+          <t>24001929.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>18265933.7</t>
+          <t>18117379.86</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-6789559</t>
+          <t>-9417027</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1034266.833169591</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-363210.27</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>785294.6850096433</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-584052.1298700683</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>14897065</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>110.0</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-9.27</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-8.64</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>99.2</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>90.678</t>
+          <t>109.187</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.65</t>
+          <t>-29.23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>99.82000000000001</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>99.72</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>102.18</t>
+          <t>101.95</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.55</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34336416.92374101</t>
+          <t>34319188.7349138</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>18569544.4</t>
+          <t>16438424.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23110350.3</t>
+          <t>23227983.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>18738868.34</t>
+          <t>18265933.7</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4540805</t>
+          <t>-6789559</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1288353.579970241</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>393582.92</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>1034266.833169591</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-363210.2742339857</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>10899290</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>110.0</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-10.36</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-9.27</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>99.8</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>202.457</t>
+          <t>90.678</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>-19.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>99.82000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>99.83</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.18</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.52</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-117.55</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34336416.92374101</t>
+          <t>34319188.7349138</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>26480263.0</t>
+          <t>18569544.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23736620.0</t>
+          <t>23110350.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>19242893.34</t>
+          <t>18738868.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2743643</t>
+          <t>-4540805</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1451039.154113366</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>1670380.53</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>1288353.579970241</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>393582.9221830554</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>8941894</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>110.0</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-10.45</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-10.36</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>5.51</t>
-        </is>
-      </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>99.7</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>98.6</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>181.83</t>
+          <t>202.457</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.83</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.51</t>
+          <t>103.52</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-119.38</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34336416.92374101</t>
+          <t>34319188.7349138</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>35759848.6</t>
+          <t>26480263.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22584742.9</t>
+          <t>23736620.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>19380974.5</t>
+          <t>19242893.34</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>13175105</t>
+          <t>2743643</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1411158.904500055</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>2249919.94</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>1451039.154113366</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>1670380.526986577</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>20000034</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>110.0</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-9.09</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-10.45</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>239.119</t>
+          <t>181.83</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>99.96</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>102.99</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.47</t>
+          <t>103.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-121.79</t>
+          <t>-119.38</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34336416.92374101</t>
+          <t>34319188.7349138</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>33418956.2</t>
+          <t>35759848.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>21669007.2</t>
+          <t>22584742.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19787904.64</t>
+          <t>19380974.5</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>11749949</t>
+          <t>13175105</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1258656.897391115</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>3191815.58</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>1411158.904500055</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>2249919.943599228</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>18186227</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>110.0</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-8.64</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-9.09</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>211.11</t>
+          <t>239.119</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3088,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3098,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.60</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.96</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.99</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.43</t>
+          <t>103.47</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.87</t>
+          <t>-121.79</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34336416.92374101</t>
+          <t>34319188.7349138</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>21554889.0</t>
+          <t>24164678.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30017543.0</t>
+          <t>33418956.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20200254.1</t>
+          <t>21669007.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>20264334.1</t>
+          <t>19787904.64</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>9817288</t>
+          <t>11749949</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>907173.5011915436</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>3782839.03</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>1258656.897391115</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>3191815.576488756</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>24164678</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>110.0</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-7.73</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-8.64</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>470.424</t>
+          <t>211.11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3524,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3534,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>37.80</t>
+          <t>48.60</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>100.56</t>
+          <t>100.88</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>99.84</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>103.46</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.43</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-128.50</t>
+          <t>-124.87</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,172 +3720,172 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34336416.92374101</t>
+          <t>34319188.7349138</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>48495487.0</t>
+          <t>21554889.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>27651156.2</t>
+          <t>30017543.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20066315.5</t>
+          <t>20200254.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>20877613.24</t>
+          <t>20264334.1</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7584840</t>
+          <t>9817288</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>384325.22296158</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>4771677.11</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>907173.5011915436</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>3782839.031456344</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>21554889</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>110.0</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-6.36</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-7.73</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
           <t>103.5</t>
@@ -3858,25 +3893,30 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>651.618</t>
+          <t>470.424</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3960,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>37.80</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.84</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.46</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.34</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-132.10</t>
+          <t>-128.50</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,172 +4156,172 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34336416.92374101</t>
+          <t>34319188.7349138</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>66397962.0</t>
+          <t>48495487.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20992977.0</t>
+          <t>27651156.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>16244706.1</t>
+          <t>20066315.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>20629028.38</t>
+          <t>20877613.24</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4748270</t>
+          <t>7584840</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-413375.1199286837</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>3127393.25</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>384325.22296158</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>4771677.10885803</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>48495487</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>110.0</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-7.73</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-6.36</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
           <t>103.0</t>
@@ -4289,25 +4329,30 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>65.452</t>
+          <t>651.618</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>32.37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>99.02000000000001</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>99.61</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>103.89</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.34</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-134.44</t>
+          <t>-132.10</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34336416.92374101</t>
+          <t>34319188.7349138</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6481765.0</t>
+          <t>66397962.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>9409637.2</t>
+          <t>20992977.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>11476200.4</t>
+          <t>16244706.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>21347947.28</t>
+          <t>20629028.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2066563</t>
+          <t>4748270</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1057151.187417239</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-1251398.63</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-413375.1199286837</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>3127393.25125837</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>66397962</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>110.0</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-10.00</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-7.73</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>71.787</t>
+          <t>65.452</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.96</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.04</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>99.14</t>
+          <t>99.02000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>99.61</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>104.14</t>
+          <t>103.89</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.27</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-135.72</t>
+          <t>-134.44</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34336416.92374101</t>
+          <t>34319188.7349138</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7157612.0</t>
+          <t>6481765.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>9919058.2</t>
+          <t>9409637.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12549366.3</t>
+          <t>11476200.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>21865999.16</t>
+          <t>21347947.28</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2630308</t>
+          <t>-2066563</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1021833.471363163</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-1042530.25</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1057151.187417239</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-1251398.62571466</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>6481765</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>110.0</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-9.64</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-10.00</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>97.646</t>
+          <t>71.787</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-20.96</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-11.59</t>
+          <t>-12.04</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>99.08000000000001</t>
+          <t>99.14</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>99.92</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>104.36</t>
+          <t>104.14</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>103.27</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>11.87</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-137.02</t>
+          <t>-135.72</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34336416.92374101</t>
+          <t>34319188.7349138</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9722955.0</t>
+          <t>7157612.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>10382965.2</t>
+          <t>9919058.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>13126733.5</t>
+          <t>12549366.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>22279772.86</t>
+          <t>21865999.16</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2743768</t>
+          <t>-2630308</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1018070.420875835</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-779325.8100000001</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1021833.471363163</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-1042530.249043465</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>7157612</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>110.0</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-9.18</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-9.64</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>5.51</t>
-        </is>
-      </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>5.47</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>99.9</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>99.4</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>149.664</t>
+          <t>87.367</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>-47.58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.58</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>99.75</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>101.74</t>
+          <t>101.51</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.62</t>
+          <t>103.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>33.20</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-114.68</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34319188.7349138</t>
+          <t>34288839.42395982</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>14584902.0</t>
+          <t>12703085.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>24001929.1</t>
+          <t>24231467.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>18117379.86</t>
+          <t>17755634.02</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-9417027</t>
+          <t>-11528381</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>785294.6850096433</t>
+          <t>482474.8795360716</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-584052.1298700683</t>
+          <t>-1183034.050568573</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>14897065</v>
+        <v>8777146</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>109.187</t>
+          <t>149.664</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-29.23</t>
+          <t>-39.23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,42 +1450,42 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1495,32 +1495,32 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>99.72</t>
+          <t>99.75</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>101.95</t>
+          <t>101.74</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>103.62</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34319188.7349138</t>
+          <t>34288839.42395982</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>16438424.6</t>
+          <t>14584902.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23227983.8</t>
+          <t>24001929.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>18265933.7</t>
+          <t>18117379.86</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-6789559</t>
+          <t>-9417027</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1034266.833169591</t>
+          <t>785294.6850096433</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-363210.2742339857</t>
+          <t>-584052.1298700683</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>10899290</v>
+        <v>14897065</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>90.678</t>
+          <t>109.187</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.65</t>
+          <t>-29.23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>99.82000000000001</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>99.72</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>102.18</t>
+          <t>101.95</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.55</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34319188.7349138</t>
+          <t>34288839.42395982</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>18569544.4</t>
+          <t>16438424.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23110350.3</t>
+          <t>23227983.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>18738868.34</t>
+          <t>18265933.7</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4540805</t>
+          <t>-6789559</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1288353.579970241</t>
+          <t>1034266.833169591</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>393582.9221830554</t>
+          <t>-363210.2742339857</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>8941894</v>
+        <v>10899290</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>202.457</t>
+          <t>90.678</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>-19.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>99.82000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>99.83</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.18</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.52</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-117.55</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34319188.7349138</t>
+          <t>34288839.42395982</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>26480263.0</t>
+          <t>18569544.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23736620.0</t>
+          <t>23110350.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>19242893.34</t>
+          <t>18738868.34</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2743643</t>
+          <t>-4540805</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1451039.154113366</t>
+          <t>1288353.579970241</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1670380.526986577</t>
+          <t>393582.9221830554</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>20000034</v>
+        <v>8941894</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>181.83</t>
+          <t>202.457</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.83</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.51</t>
+          <t>103.52</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-119.38</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34319188.7349138</t>
+          <t>34288839.42395982</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>35759848.6</t>
+          <t>26480263.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>22584742.9</t>
+          <t>23736620.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19380974.5</t>
+          <t>19242893.34</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>13175105</t>
+          <t>2743643</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1411158.904500055</t>
+          <t>1451039.154113366</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>2249919.943599228</t>
+          <t>1670380.526986577</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>18186227</v>
+        <v>20000034</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>239.119</t>
+          <t>181.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>99.96</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>102.99</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.47</t>
+          <t>103.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-121.79</t>
+          <t>-119.38</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34319188.7349138</t>
+          <t>34288839.42395982</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>33418956.2</t>
+          <t>35759848.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>21669007.2</t>
+          <t>22584742.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19787904.64</t>
+          <t>19380974.5</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>11749949</t>
+          <t>13175105</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1258656.897391115</t>
+          <t>1411158.904500055</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>3191815.576488756</t>
+          <t>2249919.943599228</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>24164678</v>
+        <v>18186227</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>100.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>211.11</t>
+          <t>239.119</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>48.60</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.96</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.99</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.43</t>
+          <t>103.47</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-124.87</t>
+          <t>-121.79</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34319188.7349138</t>
+          <t>34288839.42395982</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>21554889.0</t>
+          <t>24164678.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>30017543.0</t>
+          <t>33418956.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20200254.1</t>
+          <t>21669007.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>20264334.1</t>
+          <t>19787904.64</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>9817288</t>
+          <t>11749949</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>907173.5011915436</t>
+          <t>1258656.897391115</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>3782839.031456344</t>
+          <t>3191815.576488756</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>21554889</v>
+        <v>24164678</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>470.424</t>
+          <t>211.11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>37.80</t>
+          <t>48.60</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>100.56</t>
+          <t>100.88</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>99.84</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>103.46</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.43</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-128.50</t>
+          <t>-124.87</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34319188.7349138</t>
+          <t>34288839.42395982</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>48495487.0</t>
+          <t>21554889.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>27651156.2</t>
+          <t>30017543.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20066315.5</t>
+          <t>20200254.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>20877613.24</t>
+          <t>20264334.1</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7584840</t>
+          <t>9817288</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>384325.22296158</t>
+          <t>907173.5011915436</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>4771677.10885803</t>
+          <t>3782839.031456344</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>48495487</v>
+        <v>21554889</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>651.618</t>
+          <t>470.424</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>37.80</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.84</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.46</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.34</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-132.10</t>
+          <t>-128.50</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34319188.7349138</t>
+          <t>34288839.42395982</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>66397962.0</t>
+          <t>48495487.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20992977.0</t>
+          <t>27651156.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16244706.1</t>
+          <t>20066315.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>20629028.38</t>
+          <t>20877613.24</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4748270</t>
+          <t>7584840</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-413375.1199286837</t>
+          <t>384325.22296158</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>3127393.25125837</t>
+          <t>4771677.10885803</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>66397962</v>
+        <v>48495487</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,17 +4695,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>101.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>65.452</t>
+          <t>651.618</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>32.37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>99.02000000000001</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>99.61</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>103.89</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.34</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-134.44</t>
+          <t>-132.10</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34319188.7349138</t>
+          <t>34288839.42395982</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6481765.0</t>
+          <t>66397962.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>9409637.2</t>
+          <t>20992977.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>11476200.4</t>
+          <t>16244706.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>21347947.28</t>
+          <t>20629028.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2066563</t>
+          <t>4748270</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1057151.187417239</t>
+          <t>-413375.1199286837</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1251398.62571466</t>
+          <t>3127393.25125837</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>6481765</v>
+        <v>66397962</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>71.787</t>
+          <t>65.452</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.96</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.04</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>99.14</t>
+          <t>99.02000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>99.61</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>104.14</t>
+          <t>103.89</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.27</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-135.72</t>
+          <t>-134.44</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34319188.7349138</t>
+          <t>34288839.42395982</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7157612.0</t>
+          <t>6481765.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>9919058.2</t>
+          <t>9409637.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>12549366.3</t>
+          <t>11476200.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21865999.16</t>
+          <t>21347947.28</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2630308</t>
+          <t>-2066563</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1021833.471363163</t>
+          <t>-1057151.187417239</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1042530.249043465</t>
+          <t>-1251398.62571466</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>7157612</v>
+        <v>6481765</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.64</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>236.602</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>87.367</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-32.49</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,22 +1014,22 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1039,52 +1039,52 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>99.58</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>99.92</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>101.51</t>
+          <t>101.31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.66</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.68</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34288839.42395982</t>
+          <t>34291187.49283668</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>12703085.8</t>
+          <t>13493451.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>24231467.2</t>
+          <t>19986857.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>17755634.02</t>
+          <t>17696692.44</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-11528381</t>
+          <t>-6493405</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>482474.8795360716</t>
+          <t>341379.9874853975</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1183034.050568573</t>
+          <t>-434641.9187933095</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>8777146</v>
+        <v>23951861</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>101.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>149.664</t>
+          <t>87.367</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>-47.58</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.58</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>99.75</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>101.74</t>
+          <t>101.51</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.62</t>
+          <t>103.66</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>33.20</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-114.68</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34288839.42395982</t>
+          <t>34291187.49283668</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>14584902.0</t>
+          <t>12703085.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24001929.1</t>
+          <t>24231467.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>18117379.86</t>
+          <t>17755634.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-9417027</t>
+          <t>-11528381</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>785294.6850096433</t>
+          <t>482474.8795360716</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-584052.1298700683</t>
+          <t>-1183034.050568573</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>14897065</v>
+        <v>8777146</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>109.187</t>
+          <t>149.664</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-29.23</t>
+          <t>-39.23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,42 +1886,42 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>99.72</t>
+          <t>99.75</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>101.95</t>
+          <t>101.74</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>103.62</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34288839.42395982</t>
+          <t>34291187.49283668</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>16438424.6</t>
+          <t>14584902.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23227983.8</t>
+          <t>24001929.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>18265933.7</t>
+          <t>18117379.86</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-6789559</t>
+          <t>-9417027</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1034266.833169591</t>
+          <t>785294.6850096433</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-363210.2742339857</t>
+          <t>-584052.1298700683</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>10899290</v>
+        <v>14897065</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>90.678</t>
+          <t>109.187</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.65</t>
+          <t>-29.23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>99.82000000000001</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>99.72</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>102.18</t>
+          <t>101.95</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.55</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34288839.42395982</t>
+          <t>34291187.49283668</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>18569544.4</t>
+          <t>16438424.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23110350.3</t>
+          <t>23227983.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>18738868.34</t>
+          <t>18265933.7</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4540805</t>
+          <t>-6789559</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1288353.579970241</t>
+          <t>1034266.833169591</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>393582.9221830554</t>
+          <t>-363210.2742339857</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>8941894</v>
+        <v>10899290</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>202.457</t>
+          <t>90.678</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>-19.65</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>99.82000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>99.83</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.18</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.52</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-117.55</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34288839.42395982</t>
+          <t>34291187.49283668</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26480263.0</t>
+          <t>18569544.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23736620.0</t>
+          <t>23110350.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19242893.34</t>
+          <t>18738868.34</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2743643</t>
+          <t>-4540805</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1451039.154113366</t>
+          <t>1288353.579970241</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1670380.526986577</t>
+          <t>393582.9221830554</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>20000034</v>
+        <v>8941894</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>181.83</t>
+          <t>202.457</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.83</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.51</t>
+          <t>103.52</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-119.38</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34288839.42395982</t>
+          <t>34291187.49283668</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>35759848.6</t>
+          <t>26480263.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22584742.9</t>
+          <t>23736620.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19380974.5</t>
+          <t>19242893.34</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>13175105</t>
+          <t>2743643</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1411158.904500055</t>
+          <t>1451039.154113366</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>2249919.943599228</t>
+          <t>1670380.526986577</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>18186227</v>
+        <v>20000034</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>239.119</t>
+          <t>181.83</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>99.96</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>102.99</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.47</t>
+          <t>103.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-121.79</t>
+          <t>-119.38</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34288839.42395982</t>
+          <t>34291187.49283668</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>33418956.2</t>
+          <t>35759848.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>21669007.2</t>
+          <t>22584742.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>19787904.64</t>
+          <t>19380974.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>11749949</t>
+          <t>13175105</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1258656.897391115</t>
+          <t>1411158.904500055</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>3191815.576488756</t>
+          <t>2249919.943599228</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>24164678</v>
+        <v>18186227</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>100.0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>211.11</t>
+          <t>239.119</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>48.60</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.96</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.99</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.43</t>
+          <t>103.47</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-124.87</t>
+          <t>-121.79</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34288839.42395982</t>
+          <t>34291187.49283668</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>21554889.0</t>
+          <t>24164678.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30017543.0</t>
+          <t>33418956.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20200254.1</t>
+          <t>21669007.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>20264334.1</t>
+          <t>19787904.64</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>9817288</t>
+          <t>11749949</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>907173.5011915436</t>
+          <t>1258656.897391115</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>3782839.031456344</t>
+          <t>3191815.576488756</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>21554889</v>
+        <v>24164678</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>470.424</t>
+          <t>211.11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>37.80</t>
+          <t>48.60</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>100.56</t>
+          <t>100.88</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>99.84</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>103.46</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.43</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-128.50</t>
+          <t>-124.87</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34288839.42395982</t>
+          <t>34291187.49283668</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>48495487.0</t>
+          <t>21554889.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27651156.2</t>
+          <t>30017543.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20066315.5</t>
+          <t>20200254.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>20877613.24</t>
+          <t>20264334.1</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7584840</t>
+          <t>9817288</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>384325.22296158</t>
+          <t>907173.5011915436</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>4771677.10885803</t>
+          <t>3782839.031456344</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>48495487</v>
+        <v>21554889</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>651.618</t>
+          <t>470.424</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>37.80</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.84</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.46</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.34</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-132.10</t>
+          <t>-128.50</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34288839.42395982</t>
+          <t>34291187.49283668</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>66397962.0</t>
+          <t>48495487.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20992977.0</t>
+          <t>27651156.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>16244706.1</t>
+          <t>20066315.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>20629028.38</t>
+          <t>20877613.24</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4748270</t>
+          <t>7584840</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-413375.1199286837</t>
+          <t>384325.22296158</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>3127393.25125837</t>
+          <t>4771677.10885803</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>66397962</v>
+        <v>48495487</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>101.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>65.452</t>
+          <t>651.618</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>32.37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>99.02000000000001</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>99.61</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>103.89</t>
+          <t>103.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-134.44</t>
+          <t>-132.10</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34288839.42395982</t>
+          <t>34291187.49283668</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6481765.0</t>
+          <t>66397962.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>9409637.2</t>
+          <t>20992977.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11476200.4</t>
+          <t>16244706.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21347947.28</t>
+          <t>20629028.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2066563</t>
+          <t>4748270</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1057151.187417239</t>
+          <t>-413375.1199286837</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1251398.62571466</t>
+          <t>3127393.25125837</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>6481765</v>
+        <v>66397962</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>236.602</t>
+          <t>192.142</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>99.92</t>
+          <t>100.06</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>101.31</t>
+          <t>101.25</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.76</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.03</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34291187.49283668</t>
+          <t>34284114.61158799</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>13493451.2</t>
+          <t>15618038.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>19986857.1</t>
+          <t>17093791.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>17696692.44</t>
+          <t>16033026.32</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-6493405</t>
+          <t>-1475753</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>341379.9874853975</t>
+          <t>253640.1773213683</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-434641.9187933095</t>
+          <t>-228928.7785807922</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>23951861</v>
+        <v>19564829</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,42 +1319,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>236.602</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>87.367</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-32.49</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,22 +1450,22 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1475,52 +1475,52 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>99.58</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>99.92</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>101.51</t>
+          <t>101.31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.66</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.68</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34291187.49283668</t>
+          <t>34284114.61158799</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>12703085.8</t>
+          <t>13493451.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24231467.2</t>
+          <t>19986857.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>17755634.02</t>
+          <t>17696692.44</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-11528381</t>
+          <t>-6493405</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>482474.8795360716</t>
+          <t>341379.9874853975</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1183034.050568573</t>
+          <t>-434641.9187933095</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>8777146</v>
+        <v>23951861</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>101.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>149.664</t>
+          <t>87.367</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>-47.58</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1901,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.58</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>99.75</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>101.74</t>
+          <t>101.51</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.62</t>
+          <t>103.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>33.20</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-114.68</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34291187.49283668</t>
+          <t>34284114.61158799</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>14584902.0</t>
+          <t>12703085.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24001929.1</t>
+          <t>24231467.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>18117379.86</t>
+          <t>17755634.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-9417027</t>
+          <t>-11528381</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>785294.6850096433</t>
+          <t>482474.8795360716</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-584052.1298700683</t>
+          <t>-1183034.050568573</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>14897065</v>
+        <v>8777146</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>109.187</t>
+          <t>149.664</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-29.23</t>
+          <t>-39.23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,42 +2322,42 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2367,32 +2367,32 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>99.72</t>
+          <t>99.75</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>101.95</t>
+          <t>101.74</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>103.62</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34291187.49283668</t>
+          <t>34284114.61158799</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>16438424.6</t>
+          <t>14584902.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23227983.8</t>
+          <t>24001929.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>18265933.7</t>
+          <t>18117379.86</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-6789559</t>
+          <t>-9417027</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1034266.833169591</t>
+          <t>785294.6850096433</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-363210.2742339857</t>
+          <t>-584052.1298700683</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>10899290</v>
+        <v>14897065</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>90.678</t>
+          <t>109.187</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-19.65</t>
+          <t>-29.23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>99.82000000000001</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>99.72</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>102.18</t>
+          <t>101.95</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.59</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.55</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34291187.49283668</t>
+          <t>34284114.61158799</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18569544.4</t>
+          <t>16438424.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23110350.3</t>
+          <t>23227983.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>18738868.34</t>
+          <t>18265933.7</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4540805</t>
+          <t>-6789559</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1288353.579970241</t>
+          <t>1034266.833169591</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>393582.9221830554</t>
+          <t>-363210.2742339857</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>8941894</v>
+        <v>10899290</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>202.457</t>
+          <t>90.678</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>-19.65</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>99.82000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>99.83</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.18</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.52</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-117.55</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34291187.49283668</t>
+          <t>34284114.61158799</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>26480263.0</t>
+          <t>18569544.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23736620.0</t>
+          <t>23110350.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19242893.34</t>
+          <t>18738868.34</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2743643</t>
+          <t>-4540805</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1451039.154113366</t>
+          <t>1288353.579970241</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1670380.526986577</t>
+          <t>393582.9221830554</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>20000034</v>
+        <v>8941894</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>181.83</t>
+          <t>202.457</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.83</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.51</t>
+          <t>103.52</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-119.38</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34291187.49283668</t>
+          <t>34284114.61158799</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>35759848.6</t>
+          <t>26480263.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>22584742.9</t>
+          <t>23736620.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>19380974.5</t>
+          <t>19242893.34</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>13175105</t>
+          <t>2743643</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1411158.904500055</t>
+          <t>1451039.154113366</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>2249919.943599228</t>
+          <t>1670380.526986577</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>18186227</v>
+        <v>20000034</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>239.119</t>
+          <t>181.83</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>99.96</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>102.99</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.47</t>
+          <t>103.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-121.79</t>
+          <t>-119.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34291187.49283668</t>
+          <t>34284114.61158799</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>33418956.2</t>
+          <t>35759848.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21669007.2</t>
+          <t>22584742.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>19787904.64</t>
+          <t>19380974.5</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>11749949</t>
+          <t>13175105</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1258656.897391115</t>
+          <t>1411158.904500055</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>3191815.576488756</t>
+          <t>2249919.943599228</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>24164678</v>
+        <v>18186227</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>100.0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>211.11</t>
+          <t>239.119</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>48.60</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>99.93</t>
+          <t>99.96</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.99</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.43</t>
+          <t>103.47</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-124.87</t>
+          <t>-121.79</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34291187.49283668</t>
+          <t>34284114.61158799</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>21554889.0</t>
+          <t>24164678.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>30017543.0</t>
+          <t>33418956.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20200254.1</t>
+          <t>21669007.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>20264334.1</t>
+          <t>19787904.64</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9817288</t>
+          <t>11749949</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>907173.5011915436</t>
+          <t>1258656.897391115</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>3782839.031456344</t>
+          <t>3191815.576488756</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>21554889</v>
+        <v>24164678</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>470.424</t>
+          <t>211.11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>37.80</t>
+          <t>48.60</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>100.56</t>
+          <t>100.88</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>99.84</t>
+          <t>99.93</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>103.46</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.43</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-128.50</t>
+          <t>-124.87</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34291187.49283668</t>
+          <t>34284114.61158799</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>48495487.0</t>
+          <t>21554889.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27651156.2</t>
+          <t>30017543.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20066315.5</t>
+          <t>20200254.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>20877613.24</t>
+          <t>20264334.1</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7584840</t>
+          <t>9817288</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>384325.22296158</t>
+          <t>907173.5011915436</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>4771677.10885803</t>
+          <t>3782839.031456344</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>48495487</v>
+        <v>21554889</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>651.618</t>
+          <t>470.424</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>37.80</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.56</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.84</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>103.67</t>
+          <t>103.46</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.34</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-132.10</t>
+          <t>-128.50</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34291187.49283668</t>
+          <t>34284114.61158799</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>66397962.0</t>
+          <t>48495487.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>20992977.0</t>
+          <t>27651156.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>16244706.1</t>
+          <t>20066315.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>20629028.38</t>
+          <t>20877613.24</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>4748270</t>
+          <t>7584840</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-413375.1199286837</t>
+          <t>384325.22296158</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>3127393.25125837</t>
+          <t>4771677.10885803</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>66397962</v>
+        <v>48495487</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>101.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>100.76</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>100.06</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>101.25</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>100.06</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>101.25</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>19564829.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>15618038.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>15618038.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>17093791.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>16033026.32</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>16033026.32</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-228928.7785807922</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>19564829</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>19564829.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>100.08</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>99.92</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>101.31</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>101.31</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>23951861.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>13493451.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>13493451.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>19986857.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>17696692.44</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>17696692.44</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-434641.9187933095</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>23951861</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>23951861.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>99.58</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>101.51</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>101.51</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>8777146.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>12703085.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>12703085.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>24231467.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>17755634.02</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>17755634.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1183034.050568573</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>8777146</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>8777146.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>99.47999999999999</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>99.75</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>101.74</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>101.74</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>14897065.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>14584902.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>14584902</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>24001929.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>18117379.86</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>18117379.86</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-584052.1298700683</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>14897065</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>14897065.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>99.47999999999999</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>99.72</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>101.95</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>101.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>10899290.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>16438424.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>16438424.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>23227983.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>18265933.7</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>18265933.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-363210.2742339857</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>10899290</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>10899290.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>99.82000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>99.76</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>102.18</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>102.18</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>8941894.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>18569544.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>18569544.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>23110350.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>18738868.34</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>18738868.34</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>393582.9221830554</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>8941894</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>8941894.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>100.7</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>99.83</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>102.46</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>102.46</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>20000034.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>26480263.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>26480263</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>23736620.0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>19242893.34</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>19242893.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>1670380.526986577</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>20000034</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>20000034.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>101.3</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>99.93</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>102.75</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>102.75</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>18186227.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>35759848.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>35759848.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>22584742.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>19380974.5</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>19380974.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>2249919.943599228</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>18186227</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>18186227.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>101.1</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>99.96</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>102.99</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>102.99</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>24164678.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>33418956.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>33418956.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>21669007.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>19787904.64</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>19787904.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>3191815.576488756</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>24164678</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>24164678.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>100.88</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>99.93</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>103.2</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>103.2</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>21554889.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>30017543.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>30017543</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>20200254.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>20264334.1</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>20264334.1</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>3782839.031456344</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>21554889</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>21554889.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>100.56</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>99.84</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>103.46</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>103.46</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>48495487.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>27651156.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>27651156.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>20066315.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>20877613.24</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>20877613.24</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>4771677.10885803</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>48495487</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>48495487.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>192.142</t>
+          <t>185.485</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>100.06</v>
+        <v>100.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>101.25</v>
+        <v>101.21</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.76</t>
+          <t>103.84</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>136.91</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.03</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34284114.61158799</t>
+          <t>34275835.70142857</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>15618038.2</v>
+        <v>17236697.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>17093791.3</t>
+          <t>16837560.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>16033026.32</v>
+        <v>16046320.32</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1475753</t>
+          <t>399136</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>253640.1773213683</t>
+          <t>195830.2022000024</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-228928.7785807922</t>
+          <t>-122124.6609675102</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>236.602</t>
+          <t>192.142</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>99.92</v>
+        <v>100.06</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.31</v>
+        <v>101.25</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.76</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.03</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34284114.61158799</t>
+          <t>34275835.70142857</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>13493451.2</v>
+        <v>15618038.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>19986857.1</t>
+          <t>17093791.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>17696692.44</v>
+        <v>16033026.32</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-6493405</t>
+          <t>-1475753</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>341379.9874853975</t>
+          <t>253640.1773213683</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-434641.9187933095</t>
+          <t>-228928.7785807922</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,42 +1743,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>236.602</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>87.367</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-32.49</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,22 +1874,22 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1899,48 +1899,48 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>99.58</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>99.8</v>
+        <v>99.92</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.51</v>
+        <v>101.31</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.66</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-114.68</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34284114.61158799</t>
+          <t>34275835.70142857</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>12703085.8</v>
+        <v>13493451.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24231467.2</t>
+          <t>19986857.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>17755634.02</v>
+        <v>17696692.44</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-11528381</t>
+          <t>-6493405</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>482474.8795360716</t>
+          <t>341379.9874853975</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1183034.050568573</t>
+          <t>-434641.9187933095</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>101.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>149.664</t>
+          <t>87.367</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>-47.58</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.58</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>99.75</v>
+        <v>99.8</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.74</v>
+        <v>101.51</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.62</t>
+          <t>103.66</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>33.20</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-114.68</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34284114.61158799</t>
+          <t>34275835.70142857</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>14584902</v>
+        <v>12703085.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24001929.1</t>
+          <t>24231467.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>18117379.86</v>
+        <v>17755634.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-9417027</t>
+          <t>-11528381</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>785294.6850096433</t>
+          <t>482474.8795360716</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-584052.1298700683</t>
+          <t>-1183034.050568573</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>109.187</t>
+          <t>149.664</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-29.23</t>
+          <t>-39.23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,42 +2734,42 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,29 +2778,29 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>99.72</v>
+        <v>99.75</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.95</v>
+        <v>101.74</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>103.62</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34284114.61158799</t>
+          <t>34275835.70142857</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>16438424.6</v>
+        <v>14584902</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23227983.8</t>
+          <t>24001929.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>18265933.7</v>
+        <v>18117379.86</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-6789559</t>
+          <t>-9417027</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1034266.833169591</t>
+          <t>785294.6850096433</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-363210.2742339857</t>
+          <t>-584052.1298700683</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>90.678</t>
+          <t>109.187</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.65</t>
+          <t>-29.23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>99.82000000000001</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>99.76000000000001</v>
+        <v>99.72</v>
       </c>
       <c r="AN7" t="n">
-        <v>102.18</v>
+        <v>101.95</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.59</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.55</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34284114.61158799</t>
+          <t>34275835.70142857</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>18569544.4</v>
+        <v>16438424.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23110350.3</t>
+          <t>23227983.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>18738868.34</v>
+        <v>18265933.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-4540805</t>
+          <t>-6789559</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1288353.579970241</t>
+          <t>1034266.833169591</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>393582.9221830554</t>
+          <t>-363210.2742339857</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>202.457</t>
+          <t>90.678</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>-19.65</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>99.82000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>99.83</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>102.46</v>
+        <v>102.18</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.52</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-117.55</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34284114.61158799</t>
+          <t>34275835.70142857</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>26480263</v>
+        <v>18569544.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23736620.0</t>
+          <t>23110350.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>19242893.34</v>
+        <v>18738868.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2743643</t>
+          <t>-4540805</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1451039.154113366</t>
+          <t>1288353.579970241</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1670380.526986577</t>
+          <t>393582.9221830554</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>181.83</t>
+          <t>202.457</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>99.93000000000001</v>
+        <v>99.83</v>
       </c>
       <c r="AN9" t="n">
-        <v>102.75</v>
+        <v>102.46</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.51</t>
+          <t>103.52</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-119.38</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34284114.61158799</t>
+          <t>34275835.70142857</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>35759848.6</v>
+        <v>26480263</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>22584742.9</t>
+          <t>23736620.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>19380974.5</v>
+        <v>19242893.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>13175105</t>
+          <t>2743643</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1411158.904500055</t>
+          <t>1451039.154113366</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>2249919.943599228</t>
+          <t>1670380.526986577</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>239.119</t>
+          <t>181.83</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>99.95999999999999</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>102.99</v>
+        <v>102.75</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.47</t>
+          <t>103.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-121.79</t>
+          <t>-119.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34284114.61158799</t>
+          <t>34275835.70142857</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>33418956.2</v>
+        <v>35759848.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>21669007.2</t>
+          <t>22584742.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>19787904.64</v>
+        <v>19380974.5</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>11749949</t>
+          <t>13175105</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1258656.897391115</t>
+          <t>1411158.904500055</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>3191815.576488756</t>
+          <t>2249919.943599228</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>100.0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>211.11</t>
+          <t>239.119</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>48.60</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>99.93000000000001</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="AN11" t="n">
-        <v>103.2</v>
+        <v>102.99</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.43</t>
+          <t>103.47</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-124.87</t>
+          <t>-121.79</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34284114.61158799</t>
+          <t>34275835.70142857</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>21554889.0</t>
+          <t>24164678.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>30017543</v>
+        <v>33418956.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20200254.1</t>
+          <t>21669007.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>20264334.1</v>
+        <v>19787904.64</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>9817288</t>
+          <t>11749949</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>907173.5011915436</t>
+          <t>1258656.897391115</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>3782839.031456344</t>
+          <t>3191815.576488756</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>21554889.0</t>
+          <t>24164678.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,34 +5183,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>211.11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>470.424</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>37.80</t>
+          <t>48.60</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>100.56</t>
+          <t>100.88</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>99.84</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="AN12" t="n">
-        <v>103.46</v>
+        <v>103.2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.43</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-128.50</t>
+          <t>-124.87</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34284114.61158799</t>
+          <t>34275835.70142857</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>48495487.0</t>
+          <t>21554889.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>27651156.2</v>
+        <v>30017543</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20066315.5</t>
+          <t>20200254.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>20877613.24</v>
+        <v>20264334.1</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7584840</t>
+          <t>9817288</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>384325.22296158</t>
+          <t>907173.5011915436</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>4771677.10885803</t>
+          <t>3782839.031456344</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>48495487.0</t>
+          <t>21554889.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>185.485</t>
+          <t>104.253</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>100.21</v>
+        <v>100.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>101.21</v>
+        <v>101.18</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.84</t>
+          <t>103.91</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>136.91</t>
+          <t>245.52</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.22</t>
+          <t>-105.09</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34275835.70142857</t>
+          <t>34249971.42582025</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>17236697.2</v>
+        <v>16409948</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>16837560.9</t>
+          <t>15497425.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>16046320.32</v>
+        <v>16032717.96</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>399136</t>
+          <t>912523</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>195830.2022000024</t>
+          <t>63932.69230553659</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-122124.6609675102</t>
+          <t>-661503.6121140253</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>192.142</t>
+          <t>185.485</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>100.06</v>
+        <v>100.21</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.25</v>
+        <v>101.21</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.76</t>
+          <t>103.84</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>136.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.03</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34275835.70142857</t>
+          <t>34249971.42582025</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>15618038.2</v>
+        <v>17236697.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>17093791.3</t>
+          <t>16837560.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>16033026.32</v>
+        <v>16046320.32</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1475753</t>
+          <t>399136</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>253640.1773213683</t>
+          <t>195830.2022000024</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-228928.7785807922</t>
+          <t>-122124.6609675102</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>236.602</t>
+          <t>192.142</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>99.92</v>
+        <v>100.06</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.31</v>
+        <v>101.25</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.76</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.03</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34275835.70142857</t>
+          <t>34249971.42582025</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>13493451.2</v>
+        <v>15618038.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19986857.1</t>
+          <t>17093791.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>17696692.44</v>
+        <v>16033026.32</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-6493405</t>
+          <t>-1475753</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>341379.9874853975</t>
+          <t>253640.1773213683</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-434641.9187933095</t>
+          <t>-228928.7785807922</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,42 +2173,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>236.602</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>87.367</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-32.49</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,22 +2304,22 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -2329,48 +2329,48 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>99.58</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>99.8</v>
+        <v>99.92</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.51</v>
+        <v>101.31</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.66</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-114.68</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34275835.70142857</t>
+          <t>34249971.42582025</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>12703085.8</v>
+        <v>13493451.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24231467.2</t>
+          <t>19986857.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>17755634.02</v>
+        <v>17696692.44</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-11528381</t>
+          <t>-6493405</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>482474.8795360716</t>
+          <t>341379.9874853975</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1183034.050568573</t>
+          <t>-434641.9187933095</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>101.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>149.664</t>
+          <t>87.367</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>-47.58</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.58</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>99.75</v>
+        <v>99.8</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.74</v>
+        <v>101.51</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.62</t>
+          <t>103.66</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>33.20</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-114.68</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34275835.70142857</t>
+          <t>34249971.42582025</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>14584902</v>
+        <v>12703085.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24001929.1</t>
+          <t>24231467.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>18117379.86</v>
+        <v>17755634.02</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-9417027</t>
+          <t>-11528381</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>785294.6850096433</t>
+          <t>482474.8795360716</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-584052.1298700683</t>
+          <t>-1183034.050568573</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>109.187</t>
+          <t>149.664</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-29.23</t>
+          <t>-39.23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,42 +3164,42 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3208,29 +3208,29 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>99.72</v>
+        <v>99.75</v>
       </c>
       <c r="AN7" t="n">
-        <v>101.95</v>
+        <v>101.74</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>103.62</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34275835.70142857</t>
+          <t>34249971.42582025</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>16438424.6</v>
+        <v>14584902</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23227983.8</t>
+          <t>24001929.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>18265933.7</v>
+        <v>18117379.86</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-6789559</t>
+          <t>-9417027</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1034266.833169591</t>
+          <t>785294.6850096433</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-363210.2742339857</t>
+          <t>-584052.1298700683</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>90.678</t>
+          <t>109.187</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.65</t>
+          <t>-29.23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>99.82000000000001</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>99.76000000000001</v>
+        <v>99.72</v>
       </c>
       <c r="AN8" t="n">
-        <v>102.18</v>
+        <v>101.95</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.59</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.55</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34275835.70142857</t>
+          <t>34249971.42582025</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>18569544.4</v>
+        <v>16438424.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23110350.3</t>
+          <t>23227983.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>18738868.34</v>
+        <v>18265933.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-4540805</t>
+          <t>-6789559</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1288353.579970241</t>
+          <t>1034266.833169591</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>393582.9221830554</t>
+          <t>-363210.2742339857</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>202.457</t>
+          <t>90.678</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>-19.65</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>99.82000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>99.83</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>102.46</v>
+        <v>102.18</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.52</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-117.55</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34275835.70142857</t>
+          <t>34249971.42582025</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>26480263</v>
+        <v>18569544.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23736620.0</t>
+          <t>23110350.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>19242893.34</v>
+        <v>18738868.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2743643</t>
+          <t>-4540805</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1451039.154113366</t>
+          <t>1288353.579970241</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1670380.526986577</t>
+          <t>393582.9221830554</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>181.83</t>
+          <t>202.457</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>99.93000000000001</v>
+        <v>99.83</v>
       </c>
       <c r="AN10" t="n">
-        <v>102.75</v>
+        <v>102.46</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.51</t>
+          <t>103.52</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-119.38</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34275835.70142857</t>
+          <t>34249971.42582025</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>35759848.6</v>
+        <v>26480263</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>22584742.9</t>
+          <t>23736620.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>19380974.5</v>
+        <v>19242893.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>13175105</t>
+          <t>2743643</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1411158.904500055</t>
+          <t>1451039.154113366</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2249919.943599228</t>
+          <t>1670380.526986577</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>239.119</t>
+          <t>181.83</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>99.95999999999999</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="AN11" t="n">
-        <v>102.99</v>
+        <v>102.75</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.47</t>
+          <t>103.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-121.79</t>
+          <t>-119.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34275835.70142857</t>
+          <t>34249971.42582025</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>33418956.2</v>
+        <v>35759848.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21669007.2</t>
+          <t>22584742.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>19787904.64</v>
+        <v>19380974.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>11749949</t>
+          <t>13175105</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1258656.897391115</t>
+          <t>1411158.904500055</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>3191815.576488756</t>
+          <t>2249919.943599228</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>100.0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>211.11</t>
+          <t>239.119</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>48.60</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>99.93000000000001</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="AN12" t="n">
-        <v>103.2</v>
+        <v>102.99</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.43</t>
+          <t>103.47</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-124.87</t>
+          <t>-121.79</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34275835.70142857</t>
+          <t>34249971.42582025</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>21554889.0</t>
+          <t>24164678.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>30017543</v>
+        <v>33418956.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20200254.1</t>
+          <t>21669007.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>20264334.1</v>
+        <v>19787904.64</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9817288</t>
+          <t>11749949</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>907173.5011915436</t>
+          <t>1258656.897391115</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>3782839.031456344</t>
+          <t>3191815.576488756</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>21554889.0</t>
+          <t>24164678.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>437.196</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>104.253</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>101.9</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>100.4</v>
+        <v>100.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>101.18</v>
+        <v>101.15</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.91</t>
+          <t>103.98</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>245.52</t>
+          <t>963.68</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.09</t>
+          <t>-101.49</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34249971.42582025</t>
+          <t>34298800.21367522</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>16409948</v>
+        <v>23791556.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>15497425.0</t>
+          <t>18247321.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>16032717.96</v>
+        <v>16591916.72</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>912523</t>
+          <t>5544235</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>63932.69230553659</t>
+          <t>299729.0184718022</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-661503.6121140253</t>
+          <t>1596608.812386263</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>185.485</t>
+          <t>104.253</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.9</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>100.21</v>
+        <v>100.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.21</v>
+        <v>101.18</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.84</t>
+          <t>103.91</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>136.91</t>
+          <t>245.52</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.22</t>
+          <t>-105.09</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34249971.42582025</t>
+          <t>34298800.21367522</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>17236697.2</v>
+        <v>16409948</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16837560.9</t>
+          <t>15497425.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>16046320.32</v>
+        <v>16032717.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>399136</t>
+          <t>912523</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>195830.2022000024</t>
+          <t>63932.69230553659</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-122124.6609675102</t>
+          <t>-661503.6121140253</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>192.142</t>
+          <t>185.485</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>100.06</v>
+        <v>100.21</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.25</v>
+        <v>101.21</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.76</t>
+          <t>103.84</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>136.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.03</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34249971.42582025</t>
+          <t>34298800.21367522</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>15618038.2</v>
+        <v>17236697.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17093791.3</t>
+          <t>16837560.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>16033026.32</v>
+        <v>16046320.32</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1475753</t>
+          <t>399136</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>253640.1773213683</t>
+          <t>195830.2022000024</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-228928.7785807922</t>
+          <t>-122124.6609675102</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>236.602</t>
+          <t>192.142</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>99.92</v>
+        <v>100.06</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.31</v>
+        <v>101.25</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.76</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34249971.42582025</t>
+          <t>34298800.21367522</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>13493451.2</v>
+        <v>15618038.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19986857.1</t>
+          <t>17093791.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>17696692.44</v>
+        <v>16033026.32</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-6493405</t>
+          <t>-1475753</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>341379.9874853975</t>
+          <t>253640.1773213683</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-434641.9187933095</t>
+          <t>-228928.7785807922</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,42 +2603,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>236.602</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>87.367</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-32.49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,22 +2734,22 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -2759,48 +2759,48 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>99.58</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>99.8</v>
+        <v>99.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.51</v>
+        <v>101.31</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.66</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-114.68</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34249971.42582025</t>
+          <t>34298800.21367522</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>12703085.8</v>
+        <v>13493451.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24231467.2</t>
+          <t>19986857.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>17755634.02</v>
+        <v>17696692.44</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-11528381</t>
+          <t>-6493405</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>482474.8795360716</t>
+          <t>341379.9874853975</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1183034.050568573</t>
+          <t>-434641.9187933095</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>101.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>149.664</t>
+          <t>87.367</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>-47.58</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.58</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>99.75</v>
+        <v>99.8</v>
       </c>
       <c r="AN7" t="n">
-        <v>101.74</v>
+        <v>101.51</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.62</t>
+          <t>103.66</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>33.20</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-114.68</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34249971.42582025</t>
+          <t>34298800.21367522</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>14584902</v>
+        <v>12703085.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24001929.1</t>
+          <t>24231467.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>18117379.86</v>
+        <v>17755634.02</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-9417027</t>
+          <t>-11528381</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>785294.6850096433</t>
+          <t>482474.8795360716</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-584052.1298700683</t>
+          <t>-1183034.050568573</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>109.187</t>
+          <t>149.664</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-29.23</t>
+          <t>-39.23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,42 +3594,42 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3638,29 +3638,29 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>99.72</v>
+        <v>99.75</v>
       </c>
       <c r="AN8" t="n">
-        <v>101.95</v>
+        <v>101.74</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>103.62</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34249971.42582025</t>
+          <t>34298800.21367522</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>16438424.6</v>
+        <v>14584902</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23227983.8</t>
+          <t>24001929.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>18265933.7</v>
+        <v>18117379.86</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-6789559</t>
+          <t>-9417027</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1034266.833169591</t>
+          <t>785294.6850096433</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-363210.2742339857</t>
+          <t>-584052.1298700683</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>90.678</t>
+          <t>109.187</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.65</t>
+          <t>-29.23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>99.82000000000001</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>99.76000000000001</v>
+        <v>99.72</v>
       </c>
       <c r="AN9" t="n">
-        <v>102.18</v>
+        <v>101.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.55</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34249971.42582025</t>
+          <t>34298800.21367522</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>18569544.4</v>
+        <v>16438424.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23110350.3</t>
+          <t>23227983.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>18738868.34</v>
+        <v>18265933.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4540805</t>
+          <t>-6789559</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1288353.579970241</t>
+          <t>1034266.833169591</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>393582.9221830554</t>
+          <t>-363210.2742339857</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>202.457</t>
+          <t>90.678</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>-19.65</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>99.82000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>99.83</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>102.46</v>
+        <v>102.18</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.52</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-117.55</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34249971.42582025</t>
+          <t>34298800.21367522</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>26480263</v>
+        <v>18569544.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23736620.0</t>
+          <t>23110350.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>19242893.34</v>
+        <v>18738868.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2743643</t>
+          <t>-4540805</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1451039.154113366</t>
+          <t>1288353.579970241</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1670380.526986577</t>
+          <t>393582.9221830554</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>181.83</t>
+          <t>202.457</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>99.93000000000001</v>
+        <v>99.83</v>
       </c>
       <c r="AN11" t="n">
-        <v>102.75</v>
+        <v>102.46</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.51</t>
+          <t>103.52</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-119.38</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34249971.42582025</t>
+          <t>34298800.21367522</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>35759848.6</v>
+        <v>26480263</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>22584742.9</t>
+          <t>23736620.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>19380974.5</v>
+        <v>19242893.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>13175105</t>
+          <t>2743643</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1411158.904500055</t>
+          <t>1451039.154113366</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2249919.943599228</t>
+          <t>1670380.526986577</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>239.119</t>
+          <t>181.83</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>51.39</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>99.95999999999999</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="AN12" t="n">
-        <v>102.99</v>
+        <v>102.75</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.47</t>
+          <t>103.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-121.79</t>
+          <t>-119.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34249971.42582025</t>
+          <t>34298800.21367522</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>33418956.2</v>
+        <v>35759848.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>21669007.2</t>
+          <t>22584742.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>19787904.64</v>
+        <v>19380974.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>11749949</t>
+          <t>13175105</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1258656.897391115</t>
+          <t>1411158.904500055</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>3191815.576488756</t>
+          <t>2249919.943599228</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>24164678.0</t>
+          <t>18186227.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>100.0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>437.196</t>
+          <t>156.726</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.06</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>100.62</v>
+        <v>100.84</v>
       </c>
       <c r="AN2" t="n">
-        <v>101.15</v>
+        <v>101.13</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.98</t>
+          <t>104.01</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>963.68</t>
+          <t>734.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.49</t>
+          <t>-98.21</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34298800.21367522</t>
+          <t>34284492.69559033</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>23791556.2</v>
+        <v>22233266</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>18247321.0</t>
+          <t>17863358.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>16591916.72</v>
+        <v>16748608.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5544235</t>
+          <t>4369907</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>299729.0184718022</t>
+          <t>395619.0178187264</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1596608.812386263</t>
+          <t>923014.0142268091</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>104.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,42 +1313,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>437.196</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>104.253</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>101.9</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>100.4</v>
+        <v>100.62</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.18</v>
+        <v>101.15</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.91</t>
+          <t>103.98</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>245.52</t>
+          <t>963.68</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.09</t>
+          <t>-101.49</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34298800.21367522</t>
+          <t>34284492.69559033</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>16409948</v>
+        <v>23791556.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>15497425.0</t>
+          <t>18247321.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>16032717.96</v>
+        <v>16591916.72</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>912523</t>
+          <t>5544235</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>63932.69230553659</t>
+          <t>299729.0184718022</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-661503.6121140253</t>
+          <t>1596608.812386263</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>185.485</t>
+          <t>104.253</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>100.21</v>
+        <v>100.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.21</v>
+        <v>101.18</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.84</t>
+          <t>103.91</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>136.91</t>
+          <t>245.52</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.22</t>
+          <t>-105.09</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34298800.21367522</t>
+          <t>34284492.69559033</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>17236697.2</v>
+        <v>16409948</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>16837560.9</t>
+          <t>15497425.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>16046320.32</v>
+        <v>16032717.96</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>399136</t>
+          <t>912523</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>195830.2022000024</t>
+          <t>63932.69230553659</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-122124.6609675102</t>
+          <t>-661503.6121140253</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>192.142</t>
+          <t>185.485</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>100.06</v>
+        <v>100.21</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.25</v>
+        <v>101.21</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.76</t>
+          <t>103.84</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>136.91</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.03</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34298800.21367522</t>
+          <t>34284492.69559033</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>15618038.2</v>
+        <v>17236697.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17093791.3</t>
+          <t>16837560.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>16033026.32</v>
+        <v>16046320.32</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1475753</t>
+          <t>399136</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>253640.1773213683</t>
+          <t>195830.2022000024</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-228928.7785807922</t>
+          <t>-122124.6609675102</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>236.602</t>
+          <t>192.142</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>99.92</v>
+        <v>100.06</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.31</v>
+        <v>101.25</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.76</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34298800.21367522</t>
+          <t>34284492.69559033</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>13493451.2</v>
+        <v>15618038.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19986857.1</t>
+          <t>17093791.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>17696692.44</v>
+        <v>16033026.32</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-6493405</t>
+          <t>-1475753</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>341379.9874853975</t>
+          <t>253640.1773213683</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-434641.9187933095</t>
+          <t>-228928.7785807922</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,42 +3033,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>236.602</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>87.367</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-32.49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,22 +3164,22 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -3189,48 +3189,48 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>99.58</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>99.8</v>
+        <v>99.92</v>
       </c>
       <c r="AN7" t="n">
-        <v>101.51</v>
+        <v>101.31</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.66</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-114.68</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34298800.21367522</t>
+          <t>34284492.69559033</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>12703085.8</v>
+        <v>13493451.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24231467.2</t>
+          <t>19986857.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>17755634.02</v>
+        <v>17696692.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-11528381</t>
+          <t>-6493405</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>482474.8795360716</t>
+          <t>341379.9874853975</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1183034.050568573</t>
+          <t>-434641.9187933095</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>101.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>149.664</t>
+          <t>87.367</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>-47.58</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.58</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>99.75</v>
+        <v>99.8</v>
       </c>
       <c r="AN8" t="n">
-        <v>101.74</v>
+        <v>101.51</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.62</t>
+          <t>103.66</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>33.20</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-114.68</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34298800.21367522</t>
+          <t>34284492.69559033</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>14584902</v>
+        <v>12703085.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24001929.1</t>
+          <t>24231467.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>18117379.86</v>
+        <v>17755634.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-9417027</t>
+          <t>-11528381</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>785294.6850096433</t>
+          <t>482474.8795360716</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-584052.1298700683</t>
+          <t>-1183034.050568573</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>109.187</t>
+          <t>149.664</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-29.23</t>
+          <t>-39.23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,42 +4024,42 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4068,29 +4068,29 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>99.72</v>
+        <v>99.75</v>
       </c>
       <c r="AN9" t="n">
-        <v>101.95</v>
+        <v>101.74</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>103.62</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34298800.21367522</t>
+          <t>34284492.69559033</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>16438424.6</v>
+        <v>14584902</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23227983.8</t>
+          <t>24001929.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>18265933.7</v>
+        <v>18117379.86</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-6789559</t>
+          <t>-9417027</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1034266.833169591</t>
+          <t>785294.6850096433</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-363210.2742339857</t>
+          <t>-584052.1298700683</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>90.678</t>
+          <t>109.187</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-19.65</t>
+          <t>-29.23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>99.82000000000001</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>99.76000000000001</v>
+        <v>99.72</v>
       </c>
       <c r="AN10" t="n">
-        <v>102.18</v>
+        <v>101.95</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.59</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.55</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34298800.21367522</t>
+          <t>34284492.69559033</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>18569544.4</v>
+        <v>16438424.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23110350.3</t>
+          <t>23227983.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>18738868.34</v>
+        <v>18265933.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4540805</t>
+          <t>-6789559</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1288353.579970241</t>
+          <t>1034266.833169591</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>393582.9221830554</t>
+          <t>-363210.2742339857</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>202.457</t>
+          <t>90.678</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>-19.65</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>99.82000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>99.83</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="AN11" t="n">
-        <v>102.46</v>
+        <v>102.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.52</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-117.55</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34298800.21367522</t>
+          <t>34284492.69559033</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>26480263</v>
+        <v>18569544.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23736620.0</t>
+          <t>23110350.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>19242893.34</v>
+        <v>18738868.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2743643</t>
+          <t>-4540805</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1451039.154113366</t>
+          <t>1288353.579970241</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1670380.526986577</t>
+          <t>393582.9221830554</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>181.83</t>
+          <t>202.457</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>99.93000000000001</v>
+        <v>99.83</v>
       </c>
       <c r="AN12" t="n">
-        <v>102.75</v>
+        <v>102.46</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.51</t>
+          <t>103.52</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-119.38</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34298800.21367522</t>
+          <t>34284492.69559033</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>35759848.6</v>
+        <v>26480263</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>22584742.9</t>
+          <t>23736620.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>19380974.5</v>
+        <v>19242893.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>13175105</t>
+          <t>2743643</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1411158.904500055</t>
+          <t>1451039.154113366</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2249919.943599228</t>
+          <t>1670380.526986577</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>18186227.0</t>
+          <t>20000034.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>156.726</t>
+          <t>126.465</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,269 +1014,269 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>92.06</t>
+          <t>82.54</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>104.05</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>247.67</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-95.31</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>34263692.6015625</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>20939130.4</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>18278584.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16711913.28</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>2660546</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>365285.7658711561</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>198452.8801595196</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-6.36</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>39.48</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>100.84</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>101.13</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>104.01</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>734.33</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-98.21</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>34284492.69559033</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>22233266</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>17863358.6</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>16748608.22</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>4369907</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>395619.0178187264</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>923014.0142268091</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-6.36</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>9.37</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>39.11</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>437.196</t>
+          <t>156.726</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.06</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>100.62</v>
+        <v>100.84</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.15</v>
+        <v>101.13</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.98</t>
+          <t>104.01</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>963.68</t>
+          <t>734.33</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.49</t>
+          <t>-98.21</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34284492.69559033</t>
+          <t>34263692.6015625</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>23791556.2</v>
+        <v>22233266</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>18247321.0</t>
+          <t>17863358.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>16591916.72</v>
+        <v>16748608.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5544235</t>
+          <t>4369907</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>299729.0184718022</t>
+          <t>395619.0178187264</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1596608.812386263</t>
+          <t>923014.0142268091</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>104.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,42 +1743,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>437.196</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>104.253</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>101.9</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>100.4</v>
+        <v>100.62</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.18</v>
+        <v>101.15</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.91</t>
+          <t>103.98</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>245.52</t>
+          <t>963.68</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.09</t>
+          <t>-101.49</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34284492.69559033</t>
+          <t>34263692.6015625</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>16409948</v>
+        <v>23791556.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>15497425.0</t>
+          <t>18247321.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>16032717.96</v>
+        <v>16591916.72</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>912523</t>
+          <t>5544235</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>63932.69230553659</t>
+          <t>299729.0184718022</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-661503.6121140253</t>
+          <t>1596608.812386263</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>185.485</t>
+          <t>104.253</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>100.21</v>
+        <v>100.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.21</v>
+        <v>101.18</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.84</t>
+          <t>103.91</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>136.91</t>
+          <t>245.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.22</t>
+          <t>-105.09</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34284492.69559033</t>
+          <t>34263692.6015625</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>17236697.2</v>
+        <v>16409948</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16837560.9</t>
+          <t>15497425.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>16046320.32</v>
+        <v>16032717.96</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>399136</t>
+          <t>912523</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>195830.2022000024</t>
+          <t>63932.69230553659</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-122124.6609675102</t>
+          <t>-661503.6121140253</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>192.142</t>
+          <t>185.485</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>100.06</v>
+        <v>100.21</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.25</v>
+        <v>101.21</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.76</t>
+          <t>103.84</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>136.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.03</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34284492.69559033</t>
+          <t>34263692.6015625</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>15618038.2</v>
+        <v>17236697.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17093791.3</t>
+          <t>16837560.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>16033026.32</v>
+        <v>16046320.32</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1475753</t>
+          <t>399136</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>253640.1773213683</t>
+          <t>195830.2022000024</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-228928.7785807922</t>
+          <t>-122124.6609675102</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>236.602</t>
+          <t>192.142</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>99.92</v>
+        <v>100.06</v>
       </c>
       <c r="AN7" t="n">
-        <v>101.31</v>
+        <v>101.25</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.76</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.03</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34284492.69559033</t>
+          <t>34263692.6015625</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>13493451.2</v>
+        <v>15618038.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19986857.1</t>
+          <t>17093791.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>17696692.44</v>
+        <v>16033026.32</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-6493405</t>
+          <t>-1475753</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>341379.9874853975</t>
+          <t>253640.1773213683</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-434641.9187933095</t>
+          <t>-228928.7785807922</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,42 +3463,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>236.602</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>87.367</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-32.49</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,22 +3594,22 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -3619,48 +3619,48 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>99.58</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>99.8</v>
+        <v>99.92</v>
       </c>
       <c r="AN8" t="n">
-        <v>101.51</v>
+        <v>101.31</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.66</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-114.68</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34284492.69559033</t>
+          <t>34263692.6015625</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>12703085.8</v>
+        <v>13493451.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24231467.2</t>
+          <t>19986857.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>17755634.02</v>
+        <v>17696692.44</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-11528381</t>
+          <t>-6493405</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>482474.8795360716</t>
+          <t>341379.9874853975</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1183034.050568573</t>
+          <t>-434641.9187933095</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>101.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>149.664</t>
+          <t>87.367</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>-47.58</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.58</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>99.75</v>
+        <v>99.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>101.74</v>
+        <v>101.51</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.62</t>
+          <t>103.66</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>33.20</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-114.68</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34284492.69559033</t>
+          <t>34263692.6015625</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>14584902</v>
+        <v>12703085.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24001929.1</t>
+          <t>24231467.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>18117379.86</v>
+        <v>17755634.02</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-9417027</t>
+          <t>-11528381</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>785294.6850096433</t>
+          <t>482474.8795360716</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-584052.1298700683</t>
+          <t>-1183034.050568573</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,17 +4276,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>109.187</t>
+          <t>149.664</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-29.23</t>
+          <t>-39.23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,42 +4454,42 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4498,29 +4498,29 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>99.72</v>
+        <v>99.75</v>
       </c>
       <c r="AN10" t="n">
-        <v>101.95</v>
+        <v>101.74</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>103.62</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34284492.69559033</t>
+          <t>34263692.6015625</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>16438424.6</v>
+        <v>14584902</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23227983.8</t>
+          <t>24001929.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>18265933.7</v>
+        <v>18117379.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-6789559</t>
+          <t>-9417027</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1034266.833169591</t>
+          <t>785294.6850096433</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-363210.2742339857</t>
+          <t>-584052.1298700683</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>90.678</t>
+          <t>109.187</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-19.65</t>
+          <t>-29.23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>99.82000000000001</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>99.76000000000001</v>
+        <v>99.72</v>
       </c>
       <c r="AN11" t="n">
-        <v>102.18</v>
+        <v>101.95</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.59</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.55</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34284492.69559033</t>
+          <t>34263692.6015625</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>18569544.4</v>
+        <v>16438424.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23110350.3</t>
+          <t>23227983.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>18738868.34</v>
+        <v>18265933.7</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4540805</t>
+          <t>-6789559</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1288353.579970241</t>
+          <t>1034266.833169591</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>393582.9221830554</t>
+          <t>-363210.2742339857</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>202.457</t>
+          <t>90.678</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>-19.65</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>100.7</t>
+          <t>99.82000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>99.83</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="AN12" t="n">
-        <v>102.46</v>
+        <v>102.18</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.52</t>
+          <t>103.55</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-117.55</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34284492.69559033</t>
+          <t>34263692.6015625</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>26480263</v>
+        <v>18569544.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23736620.0</t>
+          <t>23110350.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>19242893.34</v>
+        <v>18738868.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2743643</t>
+          <t>-4540805</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1451039.154113366</t>
+          <t>1288353.579970241</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1670380.526986577</t>
+          <t>393582.9221830554</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>20000034.0</t>
+          <t>8941894.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.36</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>93.449</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>126.465</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>82.54</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>101.08</v>
+        <v>101.26</v>
       </c>
       <c r="AN2" t="n">
-        <v>101.11</v>
+        <v>101.09</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>104.05</t>
+          <t>104.08</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>247.67</t>
+          <t>146.84</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-92.58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34263692.6015625</t>
+          <t>34235658.58510639</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>20939130.4</v>
+        <v>19073908.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>18278584.3</t>
+          <t>18155302.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>16711913.28</v>
+        <v>16618262.3</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2660546</t>
+          <t>918605</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>365285.7658711561</t>
+          <t>221276.1079384292</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>198452.8801595196</t>
+          <t>-570777.0106915683</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
           <t>103.0</t>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>156.726</t>
+          <t>126.465</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,264 +1449,264 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>92.06</t>
+          <t>82.54</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>104.05</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>247.67</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-95.31</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>34235658.58510639</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>20939130.4</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>18278584.3</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>16711913.28</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>2660546</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>365285.7658711561</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>198452.8801595196</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>9.42</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>41.15</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>9952</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>100.84</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>101.13</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>104.01</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>734.33</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-98.21</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>34263692.6015625</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>22233266</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>17863358.6</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16748608.22</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>4369907</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>395619.0178187264</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>923014.0142268091</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>-6.36</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>9.37</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>39.48</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>437.196</t>
+          <t>156.726</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.06</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>100.62</v>
+        <v>100.84</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.15</v>
+        <v>101.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.98</t>
+          <t>104.01</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>963.68</t>
+          <t>734.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.49</t>
+          <t>-98.21</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34263692.6015625</t>
+          <t>34235658.58510639</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>23791556.2</v>
+        <v>22233266</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18247321.0</t>
+          <t>17863358.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>16591916.72</v>
+        <v>16748608.22</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5544235</t>
+          <t>4369907</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>299729.0184718022</t>
+          <t>395619.0178187264</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1596608.812386263</t>
+          <t>923014.0142268091</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>104.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,42 +2173,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>437.196</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>104.253</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>101.9</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>100.4</v>
+        <v>100.62</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.18</v>
+        <v>101.15</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.91</t>
+          <t>103.98</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>245.52</t>
+          <t>963.68</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.09</t>
+          <t>-101.49</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34263692.6015625</t>
+          <t>34235658.58510639</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>16409948</v>
+        <v>23791556.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>15497425.0</t>
+          <t>18247321.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>16032717.96</v>
+        <v>16591916.72</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>912523</t>
+          <t>5544235</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>63932.69230553659</t>
+          <t>299729.0184718022</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-661503.6121140253</t>
+          <t>1596608.812386263</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2436,17 +2436,17 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>185.485</t>
+          <t>104.253</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>100.21</v>
+        <v>100.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.21</v>
+        <v>101.18</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.84</t>
+          <t>103.91</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>136.91</t>
+          <t>245.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.22</t>
+          <t>-105.09</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34263692.6015625</t>
+          <t>34235658.58510639</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>17236697.2</v>
+        <v>16409948</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16837560.9</t>
+          <t>15497425.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>16046320.32</v>
+        <v>16032717.96</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>399136</t>
+          <t>912523</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>195830.2022000024</t>
+          <t>63932.69230553659</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-122124.6609675102</t>
+          <t>-661503.6121140253</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>192.142</t>
+          <t>185.485</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>100.06</v>
+        <v>100.21</v>
       </c>
       <c r="AN7" t="n">
-        <v>101.25</v>
+        <v>101.21</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.76</t>
+          <t>103.84</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>136.91</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.03</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34263692.6015625</t>
+          <t>34235658.58510639</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>15618038.2</v>
+        <v>17236697.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17093791.3</t>
+          <t>16837560.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>16033026.32</v>
+        <v>16046320.32</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1475753</t>
+          <t>399136</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>253640.1773213683</t>
+          <t>195830.2022000024</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-228928.7785807922</t>
+          <t>-122124.6609675102</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>236.602</t>
+          <t>192.142</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>99.92</v>
+        <v>100.06</v>
       </c>
       <c r="AN8" t="n">
-        <v>101.31</v>
+        <v>101.25</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.76</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34263692.6015625</t>
+          <t>34235658.58510639</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>13493451.2</v>
+        <v>15618038.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19986857.1</t>
+          <t>17093791.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>17696692.44</v>
+        <v>16033026.32</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-6493405</t>
+          <t>-1475753</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>341379.9874853975</t>
+          <t>253640.1773213683</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-434641.9187933095</t>
+          <t>-228928.7785807922</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3726,17 +3726,17 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,42 +3893,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>236.602</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>87.367</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-32.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,17 +4029,17 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -4049,48 +4049,48 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>99.58</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>99.8</v>
+        <v>99.92</v>
       </c>
       <c r="AN9" t="n">
-        <v>101.51</v>
+        <v>101.31</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.66</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-114.68</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34263692.6015625</t>
+          <t>34235658.58510639</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>12703085.8</v>
+        <v>13493451.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24231467.2</t>
+          <t>19986857.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>17755634.02</v>
+        <v>17696692.44</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-11528381</t>
+          <t>-6493405</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>482474.8795360716</t>
+          <t>341379.9874853975</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1183034.050568573</t>
+          <t>-434641.9187933095</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>101.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>149.664</t>
+          <t>87.367</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>-47.58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.58</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>99.75</v>
+        <v>99.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>101.74</v>
+        <v>101.51</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.62</t>
+          <t>103.66</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>33.20</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-114.68</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34263692.6015625</t>
+          <t>34235658.58510639</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>14584902</v>
+        <v>12703085.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>24001929.1</t>
+          <t>24231467.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>18117379.86</v>
+        <v>17755634.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-9417027</t>
+          <t>-11528381</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>785294.6850096433</t>
+          <t>482474.8795360716</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-584052.1298700683</t>
+          <t>-1183034.050568573</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4586,17 +4586,17 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>109.187</t>
+          <t>149.664</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-29.23</t>
+          <t>-39.23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,37 +4889,37 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4928,29 +4928,29 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>99.72</v>
+        <v>99.75</v>
       </c>
       <c r="AN11" t="n">
-        <v>101.95</v>
+        <v>101.74</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>103.62</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34263692.6015625</t>
+          <t>34235658.58510639</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>16438424.6</v>
+        <v>14584902</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23227983.8</t>
+          <t>24001929.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>18265933.7</v>
+        <v>18117379.86</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-6789559</t>
+          <t>-9417027</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1034266.833169591</t>
+          <t>785294.6850096433</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-363210.2742339857</t>
+          <t>-584052.1298700683</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>90.678</t>
+          <t>109.187</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-19.65</t>
+          <t>-29.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>99.82000000000001</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>99.76000000000001</v>
+        <v>99.72</v>
       </c>
       <c r="AN12" t="n">
-        <v>102.18</v>
+        <v>101.95</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.55</t>
+          <t>103.59</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.55</t>
+          <t>-116.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34263692.6015625</t>
+          <t>34235658.58510639</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>18569544.4</v>
+        <v>16438424.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23110350.3</t>
+          <t>23227983.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>18738868.34</v>
+        <v>18265933.7</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4540805</t>
+          <t>-6789559</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1288353.579970241</t>
+          <t>1034266.833169591</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>393582.9221830554</t>
+          <t>-363210.2742339857</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>8941894.0</t>
+          <t>10899290.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5446,17 +5446,17 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.36</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>93.449</t>
+          <t>68.439</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.41</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,37 +1019,33 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>77.78</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.83</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1058,30 +1054,26 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>101.26</v>
+        <v>101.44</v>
       </c>
       <c r="AN2" t="n">
-        <v>101.09</v>
+        <v>101.05</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>104.08</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>146.84</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
+          <t>92.57</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.36</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-92.58</t>
+          <t>-90.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34235658.58510639</t>
+          <t>34202192.15651558</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>19073908.2</v>
+        <v>18335692.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>18155302.7</t>
+          <t>17372820.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>16618262.3</v>
+        <v>16470596.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>918605</t>
+          <t>962872</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>221276.1079384292</t>
+          <t>-11156.53313210487</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-570777.0106915683</t>
+          <t>-1289536.059020042</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1206,17 +1198,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>103.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,42 +1305,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>93.449</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>126.465</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,69 +1441,61 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>82.54</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
+          <t>77.78</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2.01</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>101.08</v>
+        <v>101.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.11</v>
+        <v>101.09</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>104.05</t>
+          <t>104.08</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>247.67</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
+          <t>146.84</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.28</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-92.58</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34235658.58510639</t>
+          <t>34202192.15651558</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>20939130.4</v>
+        <v>19073908.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>18278584.3</t>
+          <t>18155302.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>16711913.28</v>
+        <v>16618262.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2660546</t>
+          <t>918605</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>365285.7658711561</t>
+          <t>221276.1079384292</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>198452.8801595196</t>
+          <t>-570777.0106915683</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,14 +1680,14 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
           <t>103.0</t>
@@ -1711,7 +1695,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>156.726</t>
+          <t>126.465</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,264 +1863,256 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>92.06</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
+          <t>82.54</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.09</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>104.05</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>247.67</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-95.31</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>34202192.15651558</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>20939130.4</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>18278584.3</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>16711913.28</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>2660546</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>365285.7658711561</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>198452.8801595196</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>42.22</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>100.84</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>101.13</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>104.01</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>734.33</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-98.21</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>34235658.58510639</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>22233266</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>17863358.6</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16748608.22</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>4369907</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>395619.0178187264</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>923014.0142268091</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>9.42</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>41.15</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>9952</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2163,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>437.196</t>
+          <t>156.726</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,102 +2174,102 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>24.46</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-8.85</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>7.79</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>-0.48</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>30.38</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-7.96</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>21.72</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,69 +2285,61 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
+          <t>92.06</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.14</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>100.62</v>
+        <v>100.84</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.15</v>
+        <v>101.13</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.98</t>
+          <t>104.01</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>963.68</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
+          <t>734.33</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.49</t>
+          <t>-98.21</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34235658.58510639</t>
+          <t>34202192.15651558</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>23791556.2</v>
+        <v>22233266</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>18247321.0</t>
+          <t>17863358.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>16591916.72</v>
+        <v>16748608.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5544235</t>
+          <t>4369907</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>299729.0184718022</t>
+          <t>395619.0178187264</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1596608.812386263</t>
+          <t>923014.0142268091</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>104.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,42 +2571,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>437.196</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>104.253</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,7 +2707,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2752,56 +2720,48 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
+      <c r="AH6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.96</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>101.9</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>100.4</v>
+        <v>100.62</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.18</v>
+        <v>101.15</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.91</t>
+          <t>103.98</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>245.52</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
+          <t>963.68</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.06</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.09</t>
+          <t>-101.49</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34235658.58510639</t>
+          <t>34202192.15651558</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>16409948</v>
+        <v>23791556.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>15497425.0</t>
+          <t>18247321.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>16032717.96</v>
+        <v>16591916.72</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>912523</t>
+          <t>5544235</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>63932.69230553659</t>
+          <t>299729.0184718022</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-661503.6121140253</t>
+          <t>1596608.812386263</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,7 +2951,7 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +2961,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>185.485</t>
+          <t>104.253</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,7 +3129,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,59 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>94.44</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.49</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>100.21</v>
+        <v>100.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>101.21</v>
+        <v>101.18</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.84</t>
+          <t>103.91</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>136.91</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
+          <t>245.52</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.19</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.22</t>
+          <t>-105.09</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34235658.58510639</t>
+          <t>34202192.15651558</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>17236697.2</v>
+        <v>16409948</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>16837560.9</t>
+          <t>15497425.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>16046320.32</v>
+        <v>16032717.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>399136</t>
+          <t>912523</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>195830.2022000024</t>
+          <t>63932.69230553659</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-122124.6609675102</t>
+          <t>-661503.6121140253</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3331,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3366,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3368,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3453,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3468,7 +3420,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>192.142</t>
+          <t>185.485</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,7 +3551,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,59 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>75.93</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
+          <t>94.44</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.19</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>100.06</v>
+        <v>100.21</v>
       </c>
       <c r="AN8" t="n">
-        <v>101.25</v>
+        <v>101.21</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.76</t>
+          <t>103.84</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>76.45</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
+          <t>136.91</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.31</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.03</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34235658.58510639</t>
+          <t>34202192.15651558</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>15618038.2</v>
+        <v>17236697.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17093791.3</t>
+          <t>16837560.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>16033026.32</v>
+        <v>16046320.32</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1475753</t>
+          <t>399136</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>253640.1773213683</t>
+          <t>195830.2022000024</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-228928.7785807922</t>
+          <t>-122124.6609675102</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,7 +3795,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3805,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>236.602</t>
+          <t>192.142</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,69 +3973,61 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>57.41</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
+          <t>75.93</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.7</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>99.92</v>
+        <v>100.06</v>
       </c>
       <c r="AN9" t="n">
-        <v>101.31</v>
+        <v>101.25</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.76</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>46.65</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
+          <t>76.45</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.41</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.03</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34235658.58510639</t>
+          <t>34202192.15651558</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>13493451.2</v>
+        <v>15618038.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19986857.1</t>
+          <t>17093791.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>17696692.44</v>
+        <v>16033026.32</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-6493405</t>
+          <t>-1475753</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>341379.9874853975</t>
+          <t>253640.1773213683</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-434641.9187933095</t>
+          <t>-228928.7785807922</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,7 +4212,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4286,12 +4222,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,42 +4259,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>236.602</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>87.367</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-32.49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,69 +4395,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>39.26</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
+          <t>57.41</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.16</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>99.58</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>99.8</v>
+        <v>99.92</v>
       </c>
       <c r="AN10" t="n">
-        <v>101.51</v>
+        <v>101.31</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.66</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>33.20</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.36</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
+          <t>46.65</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.49</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-114.68</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34235658.58510639</t>
+          <t>34202192.15651558</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>12703085.8</v>
+        <v>13493451.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>24231467.2</t>
+          <t>19986857.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>17755634.02</v>
+        <v>17696692.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-11528381</t>
+          <t>-6493405</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>482474.8795360716</t>
+          <t>341379.9874853975</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1183034.050568573</t>
+          <t>-434641.9187933095</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4639,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>101.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4741,11 +4669,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>6192</t>
@@ -4753,12 +4677,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>149.664</t>
+          <t>87.367</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4778,7 +4702,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4712,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>-47.58</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4863,17 +4787,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4813,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,59 +4823,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>25.19</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
+          <t>39.26</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.22</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.58</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>99.75</v>
+        <v>99.8</v>
       </c>
       <c r="AN11" t="n">
-        <v>101.74</v>
+        <v>101.51</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.62</t>
+          <t>103.66</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>25.41</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.59</t>
-        </is>
+          <t>33.20</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.55</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4876,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-114.68</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4886,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34235658.58510639</t>
+          <t>34202192.15651558</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>14584902</v>
+        <v>12703085.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24001929.1</t>
+          <t>24231467.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>18117379.86</v>
+        <v>17755634.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-9417027</t>
+          <t>-11528381</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>785294.6850096433</t>
+          <t>482474.8795360716</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-584052.1298700683</t>
+          <t>-1183034.050568573</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5051,7 +4967,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +4987,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5002,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5012,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5027,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,17 +5052,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5171,11 +5087,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>6192</t>
@@ -5183,12 +5095,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>109.187</t>
+          <t>149.664</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5110,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5120,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5130,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-29.23</t>
+          <t>-39.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5195,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5205,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,37 +5231,33 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10.37</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
+          <t>25.19</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0.27</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5358,30 +5266,26 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>99.72</v>
+        <v>99.75</v>
       </c>
       <c r="AN12" t="n">
-        <v>101.95</v>
+        <v>101.74</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>103.62</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>15.39</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
+          <t>25.41</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.59</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5294,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-116.90</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5304,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34235658.58510639</t>
+          <t>34202192.15651558</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>16438424.6</v>
+        <v>14584902</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23227983.8</t>
+          <t>24001929.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>18265933.7</v>
+        <v>18117379.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-6789559</t>
+          <t>-9417027</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1034266.833169591</t>
+          <t>785294.6850096433</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-363210.2742339857</t>
+          <t>-584052.1298700683</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>10899290.0</t>
+          <t>14897065.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5360,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5385,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5405,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5415,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5430,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5445,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5470,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>68.439</t>
+          <t>74.992</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>-37.81</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>59.13</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>101.44</v>
+        <v>101.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>101.05</v>
+        <v>101.01</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>104.11</t>
+          <t>104.12</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>92.57</t>
+          <t>56.06</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-90.35</t>
+          <t>-88.78</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34202192.15651558</t>
+          <t>34170130.33239038</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>18335692.4</v>
+        <v>10736586</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>17372820.2</t>
+          <t>17264071.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>16470596.92</v>
+        <v>16342819.74</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>962872</t>
+          <t>-6527485</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-11156.53313210487</t>
+          <t>-273151.3536309307</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1289536.059020042</t>
+          <t>-1714122.866374472</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>93.449</t>
+          <t>68.439</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.41</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,38 +1436,38 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.19</v>
+        <v>-0.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1476,26 +1476,26 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>101.26</v>
+        <v>101.44</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.09</v>
+        <v>101.05</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>104.08</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>146.84</t>
+          <t>92.57</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-92.58</t>
+          <t>-90.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34202192.15651558</t>
+          <t>34170130.33239038</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>19073908.2</v>
+        <v>18335692.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>18155302.7</t>
+          <t>17372820.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>16618262.3</v>
+        <v>16470596.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>918605</t>
+          <t>962872</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>221276.1079384292</t>
+          <t>-11156.53313210487</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-570777.0106915683</t>
+          <t>-1289536.059020042</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1620,17 +1620,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>103.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,42 +1727,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>93.449</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>126.465</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>82.54</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>101.08</v>
+        <v>101.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.11</v>
+        <v>101.09</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>104.05</t>
+          <t>104.08</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>247.67</t>
+          <t>146.84</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-92.58</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34202192.15651558</t>
+          <t>34170130.33239038</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>20939130.4</v>
+        <v>19073908.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18278584.3</t>
+          <t>18155302.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>16711913.28</v>
+        <v>16618262.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2660546</t>
+          <t>918605</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>365285.7658711561</t>
+          <t>221276.1079384292</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>198452.8801595196</t>
+          <t>-570777.0106915683</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,14 +2102,14 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
           <t>103.0</t>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>156.726</t>
+          <t>126.465</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,261 +2280,261 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>92.06</t>
+          <t>82.54</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>104.05</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>247.67</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-95.31</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>34170130.33239038</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>20939130.4</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>18278584.3</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>16711913.28</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>2660546</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>365285.7658711561</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>198452.8801595196</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>5.37</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>41.61</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>9856</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>100.84</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>101.13</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>104.01</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>734.33</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-98.21</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>34202192.15651558</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>22233266</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>17863358.6</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>16748608.22</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>4369907</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>395619.0178187264</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>923014.0142268091</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>9.37</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>42.22</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>437.196</t>
+          <t>156.726</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.06</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>100.62</v>
+        <v>100.84</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.15</v>
+        <v>101.13</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.98</t>
+          <t>104.01</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>963.68</t>
+          <t>734.33</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-101.49</t>
+          <t>-98.21</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34202192.15651558</t>
+          <t>34170130.33239038</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>23791556.2</v>
+        <v>22233266</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18247321.0</t>
+          <t>17863358.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>16591916.72</v>
+        <v>16748608.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5544235</t>
+          <t>4369907</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>299729.0184718022</t>
+          <t>395619.0178187264</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1596608.812386263</t>
+          <t>923014.0142268091</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>104.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,42 +2993,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>437.196</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>104.253</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>101.9</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>100.4</v>
+        <v>100.62</v>
       </c>
       <c r="AN7" t="n">
-        <v>101.18</v>
+        <v>101.15</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.91</t>
+          <t>103.98</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>245.52</t>
+          <t>963.68</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.28</v>
+        <v>0.48</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.09</t>
+          <t>-101.49</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34202192.15651558</t>
+          <t>34170130.33239038</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>16409948</v>
+        <v>23791556.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>15497425.0</t>
+          <t>18247321.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>16032717.96</v>
+        <v>16591916.72</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>912523</t>
+          <t>5544235</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>63932.69230553659</t>
+          <t>299729.0184718022</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-661503.6121140253</t>
+          <t>1596608.812386263</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>185.485</t>
+          <t>104.253</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>100.21</v>
+        <v>100.4</v>
       </c>
       <c r="AN8" t="n">
-        <v>101.21</v>
+        <v>101.18</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.84</t>
+          <t>103.91</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>136.91</t>
+          <t>245.52</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.31</v>
+        <v>-0.19</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.22</t>
+          <t>-105.09</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34202192.15651558</t>
+          <t>34170130.33239038</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>17236697.2</v>
+        <v>16409948</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>16837560.9</t>
+          <t>15497425.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>16046320.32</v>
+        <v>16032717.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>399136</t>
+          <t>912523</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>195830.2022000024</t>
+          <t>63932.69230553659</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-122124.6609675102</t>
+          <t>-661503.6121140253</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>192.142</t>
+          <t>185.485</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,51 +3983,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.7</v>
+        <v>1.19</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>100.06</v>
+        <v>100.21</v>
       </c>
       <c r="AN9" t="n">
-        <v>101.25</v>
+        <v>101.21</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.76</t>
+          <t>103.84</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>136.91</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.41</v>
+        <v>-0.31</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.03</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34202192.15651558</t>
+          <t>34170130.33239038</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>15618038.2</v>
+        <v>17236697.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17093791.3</t>
+          <t>16837560.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>16033026.32</v>
+        <v>16046320.32</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1475753</t>
+          <t>399136</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>253640.1773213683</t>
+          <t>195830.2022000024</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-228928.7785807922</t>
+          <t>-122124.6609675102</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>236.602</t>
+          <t>192.142</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.16</v>
+        <v>0.7</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>99.92</v>
+        <v>100.06</v>
       </c>
       <c r="AN10" t="n">
-        <v>101.31</v>
+        <v>101.25</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.76</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.26</v>
+        <v>-0.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.49</v>
+        <v>-0.41</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.03</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34202192.15651558</t>
+          <t>34170130.33239038</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>13493451.2</v>
+        <v>15618038.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>19986857.1</t>
+          <t>17093791.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>17696692.44</v>
+        <v>16033026.32</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-6493405</t>
+          <t>-1475753</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>341379.9874853975</t>
+          <t>253640.1773213683</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-434641.9187933095</t>
+          <t>-228928.7785807922</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4669,7 +4669,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>6192</t>
@@ -4677,42 +4681,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>236.602</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>87.367</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-32.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4777,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4787,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4808,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>0.92</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.22</v>
+        <v>0.16</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>99.58</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>99.8</v>
+        <v>99.92</v>
       </c>
       <c r="AN11" t="n">
-        <v>101.51</v>
+        <v>101.31</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.66</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.36</v>
+        <v>-0.26</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.55</v>
+        <v>-0.49</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4876,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-114.68</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4886,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34202192.15651558</t>
+          <t>34170130.33239038</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>12703085.8</v>
+        <v>13493451.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24231467.2</t>
+          <t>19986857.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>17755634.02</v>
+        <v>17696692.44</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-11528381</t>
+          <t>-6493405</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>482474.8795360716</t>
+          <t>341379.9874853975</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1183034.050568573</t>
+          <t>-434641.9187933095</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4942,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4987,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4997,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5012,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5027,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5057,17 +5061,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>101.0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5087,7 +5091,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>6192</t>
@@ -5095,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>149.664</t>
+          <t>87.367</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5120,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5130,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-39.23</t>
+          <t>-47.58</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5205,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5226,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5241,51 +5249,51 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>39.26</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.27</v>
+        <v>-0.22</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.58</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>99.75</v>
+        <v>99.8</v>
       </c>
       <c r="AN12" t="n">
-        <v>101.74</v>
+        <v>101.51</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.62</t>
+          <t>103.66</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>33.20</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.44</v>
+        <v>-0.36</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.59</v>
+        <v>-0.55</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5294,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-114.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5304,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34202192.15651558</t>
+          <t>34170130.33239038</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>14584902</v>
+        <v>12703085.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24001929.1</t>
+          <t>24231467.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>18117379.86</v>
+        <v>17755634.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-9417027</t>
+          <t>-11528381</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>785294.6850096433</t>
+          <t>482474.8795360716</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-584052.1298700683</t>
+          <t>-1183034.050568573</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>14897065.0</t>
+          <t>8777146.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5405,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5420,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5430,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5445,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5470,17 +5478,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74.992</t>
+          <t>82.876</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-37.81</t>
+          <t>-41.47</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,261 +1014,261 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>59.13</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.49</v>
+        <v>-0.39</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>102.9</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>104.03</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>34.25</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-87.73</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>34139809.84533899</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>8468817.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>9198267.4</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>15715766.7</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16350764.5</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-6517499</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-524980.9007435892</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-1910043.409863211</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>8468817.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>5.37</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>41.37</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>9856</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="AM2" t="n">
-        <v>101.62</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>101.01</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>104.12</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>56.06</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-88.78</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>34170130.33239038</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>7689655.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>10736586</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>17264071.1</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>16342819.74</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-6527485</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-273151.3536309307</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-1714122.866374472</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>7689655.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-0.97</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>5.37</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>41.61</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>9856</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>68.439</t>
+          <t>74.992</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>-37.81</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>59.13</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>101.44</v>
+        <v>101.62</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.05</v>
+        <v>101.01</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>104.11</t>
+          <t>104.12</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>92.57</t>
+          <t>56.06</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-90.35</t>
+          <t>-88.78</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34170130.33239038</t>
+          <t>34139809.84533899</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>18335692.4</v>
+        <v>10736586</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>17372820.2</t>
+          <t>17264071.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>16470596.92</v>
+        <v>16342819.74</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>962872</t>
+          <t>-6527485</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-11156.53313210487</t>
+          <t>-273151.3536309307</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1289536.059020042</t>
+          <t>-1714122.866374472</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>93.449</t>
+          <t>68.439</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.41</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,38 +1858,38 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.19</v>
+        <v>-0.29</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1898,26 +1898,26 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>101.26</v>
+        <v>101.44</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.09</v>
+        <v>101.05</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>104.08</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>146.84</t>
+          <t>92.57</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-92.58</t>
+          <t>-90.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34170130.33239038</t>
+          <t>34139809.84533899</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>19073908.2</v>
+        <v>18335692.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18155302.7</t>
+          <t>17372820.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>16618262.3</v>
+        <v>16470596.92</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>918605</t>
+          <t>962872</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>221276.1079384292</t>
+          <t>-11156.53313210487</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-570777.0106915683</t>
+          <t>-1289536.059020042</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>103.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,42 +2149,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>93.449</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>126.465</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>82.54</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>101.08</v>
+        <v>101.26</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.11</v>
+        <v>101.09</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>104.05</t>
+          <t>104.08</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>247.67</t>
+          <t>146.84</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-92.58</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34170130.33239038</t>
+          <t>34139809.84533899</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>20939130.4</v>
+        <v>19073908.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>18278584.3</t>
+          <t>18155302.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>16711913.28</v>
+        <v>16618262.3</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2660546</t>
+          <t>918605</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>365285.7658711561</t>
+          <t>221276.1079384292</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>198452.8801595196</t>
+          <t>-570777.0106915683</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2524,14 +2524,14 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
           <t>103.0</t>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>156.726</t>
+          <t>126.465</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,261 +2702,261 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>92.06</t>
+          <t>82.54</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>104.05</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>247.67</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-95.31</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>34139809.84533899</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>20939130.4</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>18278584.3</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16711913.28</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>2660546</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>365285.7658711561</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>198452.8801595196</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>5.37</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>41.37</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>9856</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>100.84</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>101.13</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>104.01</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>734.33</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-98.21</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>34170130.33239038</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>22233266</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>17863358.6</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16748608.22</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>4369907</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>395619.0178187264</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>923014.0142268091</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>5.37</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>41.61</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>9856</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>437.196</t>
+          <t>156.726</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.06</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>100.62</v>
+        <v>100.84</v>
       </c>
       <c r="AN7" t="n">
-        <v>101.15</v>
+        <v>101.13</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.98</t>
+          <t>104.01</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>963.68</t>
+          <t>734.33</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-101.49</t>
+          <t>-98.21</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34170130.33239038</t>
+          <t>34139809.84533899</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>23791556.2</v>
+        <v>22233266</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18247321.0</t>
+          <t>17863358.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>16591916.72</v>
+        <v>16748608.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5544235</t>
+          <t>4369907</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>299729.0184718022</t>
+          <t>395619.0178187264</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1596608.812386263</t>
+          <t>923014.0142268091</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>104.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,42 +3415,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>437.196</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>104.253</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3565,47 +3565,47 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>101.9</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>100.4</v>
+        <v>100.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>101.18</v>
+        <v>101.15</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.91</t>
+          <t>103.98</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>245.52</t>
+          <t>963.68</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.28</v>
+        <v>0.48</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.09</t>
+          <t>-101.49</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34170130.33239038</t>
+          <t>34139809.84533899</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>16409948</v>
+        <v>23791556.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>15497425.0</t>
+          <t>18247321.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>16032717.96</v>
+        <v>16591916.72</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>912523</t>
+          <t>5544235</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>63932.69230553659</t>
+          <t>299729.0184718022</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-661503.6121140253</t>
+          <t>1596608.812386263</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>185.485</t>
+          <t>104.253</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,51 +3983,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>100.21</v>
+        <v>100.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>101.21</v>
+        <v>101.18</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.84</t>
+          <t>103.91</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>136.91</t>
+          <t>245.52</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.31</v>
+        <v>-0.19</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.22</t>
+          <t>-105.09</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34170130.33239038</t>
+          <t>34139809.84533899</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>17236697.2</v>
+        <v>16409948</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>16837560.9</t>
+          <t>15497425.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>16046320.32</v>
+        <v>16032717.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>399136</t>
+          <t>912523</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>195830.2022000024</t>
+          <t>63932.69230553659</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-122124.6609675102</t>
+          <t>-661503.6121140253</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>192.142</t>
+          <t>185.485</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4405,51 +4405,51 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.7</v>
+        <v>1.19</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>100.06</v>
+        <v>100.21</v>
       </c>
       <c r="AN10" t="n">
-        <v>101.25</v>
+        <v>101.21</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.76</t>
+          <t>103.84</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>136.91</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.41</v>
+        <v>-0.31</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.03</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34170130.33239038</t>
+          <t>34139809.84533899</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>15618038.2</v>
+        <v>17236697.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17093791.3</t>
+          <t>16837560.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>16033026.32</v>
+        <v>16046320.32</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1475753</t>
+          <t>399136</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>253640.1773213683</t>
+          <t>195830.2022000024</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-228928.7785807922</t>
+          <t>-122124.6609675102</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>236.602</t>
+          <t>192.142</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.16</v>
+        <v>0.7</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>99.92</v>
+        <v>100.06</v>
       </c>
       <c r="AN11" t="n">
-        <v>101.31</v>
+        <v>101.25</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.76</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.26</v>
+        <v>-0.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.49</v>
+        <v>-0.41</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.03</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34170130.33239038</t>
+          <t>34139809.84533899</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>13493451.2</v>
+        <v>15618038.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>19986857.1</t>
+          <t>17093791.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>17696692.44</v>
+        <v>16033026.32</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-6493405</t>
+          <t>-1475753</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>341379.9874853975</t>
+          <t>253640.1773213683</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-434641.9187933095</t>
+          <t>-228928.7785807922</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,42 +5103,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>236.602</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>87.367</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-32.49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-11.06</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AH12" t="n">
         <v>0.92</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.22</v>
+        <v>0.16</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>99.58</t>
+          <t>100.08</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>99.8</v>
+        <v>99.92</v>
       </c>
       <c r="AN12" t="n">
-        <v>101.51</v>
+        <v>101.31</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.66</t>
+          <t>103.7</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.36</v>
+        <v>-0.26</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.55</v>
+        <v>-0.49</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-114.68</t>
+          <t>-113.14</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34170130.33239038</t>
+          <t>34139809.84533899</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>12703085.8</v>
+        <v>13493451.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24231467.2</t>
+          <t>19986857.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>17755634.02</v>
+        <v>17696692.44</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-11528381</t>
+          <t>-6493405</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>482474.8795360716</t>
+          <t>341379.9874853975</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1183034.050568573</t>
+          <t>-434641.9187933095</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>8777146.0</t>
+          <t>23951861.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5483,17 +5483,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>101.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>100.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>152.493</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>82.876</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-41.47</t>
+          <t>-36.53</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.39</v>
+        <v>0.87</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>102.9</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>101.67</v>
+        <v>101.72</v>
       </c>
       <c r="AN2" t="n">
         <v>100.96</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>103.94</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-87.73</t>
+          <t>-86.44</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34139809.84533899</t>
+          <t>34125026.14104372</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8468817.0</t>
+          <t>15772109.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9198267.4</v>
+        <v>9733859</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>15715766.7</t>
+          <t>15336494.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>16350764.5</v>
+        <v>16314807.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-6517499</t>
+          <t>-5602635</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-524980.9007435892</t>
+          <t>-667551.5014074596</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1910043.409863211</t>
+          <t>-1451689.805058748</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>8468817.0</t>
+          <t>15772109.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>74.992</t>
+          <t>82.876</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-37.81</t>
+          <t>-41.47</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,261 +1436,261 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>59.13</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.49</v>
+        <v>-0.39</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>102.9</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>104.03</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>34.25</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-87.73</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>34125026.14104372</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>8468817.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>9198267.4</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>15715766.7</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>16350764.5</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-6517499</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-524980.9007435892</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-1910043.409863211</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>8468817.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>41.21</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="AM3" t="n">
-        <v>101.62</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>101.01</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>104.12</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>56.06</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-88.78</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>34139809.84533899</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>7689655.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>10736586</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>17264071.1</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16342819.74</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-6527485</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-273151.3536309307</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-1714122.866374472</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>7689655.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>-0.97</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>5.37</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>9856</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>68.439</t>
+          <t>74.992</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>-37.81</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>59.13</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>101.44</v>
+        <v>101.62</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.05</v>
+        <v>101.01</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>104.11</t>
+          <t>104.12</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>92.57</t>
+          <t>56.06</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-90.35</t>
+          <t>-88.78</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>34139809.84533899</t>
+          <t>34125026.14104372</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>18335692.4</v>
+        <v>10736586</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17372820.2</t>
+          <t>17264071.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>16470596.92</v>
+        <v>16342819.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>962872</t>
+          <t>-6527485</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-11156.53313210487</t>
+          <t>-273151.3536309307</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1289536.059020042</t>
+          <t>-1714122.866374472</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>93.449</t>
+          <t>68.439</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.41</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,38 +2280,38 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.19</v>
+        <v>-0.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2320,26 +2320,26 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>101.26</v>
+        <v>101.44</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.09</v>
+        <v>101.05</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>104.08</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>146.84</t>
+          <t>92.57</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-92.58</t>
+          <t>-90.35</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34139809.84533899</t>
+          <t>34125026.14104372</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>19073908.2</v>
+        <v>18335692.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>18155302.7</t>
+          <t>17372820.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>16618262.3</v>
+        <v>16470596.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>918605</t>
+          <t>962872</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>221276.1079384292</t>
+          <t>-11156.53313210487</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-570777.0106915683</t>
+          <t>-1289536.059020042</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2464,17 +2464,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>103.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,42 +2571,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>93.449</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>126.465</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>82.54</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>101.08</v>
+        <v>101.26</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.11</v>
+        <v>101.09</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>104.05</t>
+          <t>104.08</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>247.67</t>
+          <t>146.84</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-92.58</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34139809.84533899</t>
+          <t>34125026.14104372</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>20939130.4</v>
+        <v>19073908.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18278584.3</t>
+          <t>18155302.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>16711913.28</v>
+        <v>16618262.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2660546</t>
+          <t>918605</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>365285.7658711561</t>
+          <t>221276.1079384292</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>198452.8801595196</t>
+          <t>-570777.0106915683</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
           <t>103.0</t>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>156.726</t>
+          <t>126.465</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,261 +3124,261 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>92.06</t>
+          <t>82.54</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>104.05</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>247.67</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-95.31</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>34125026.14104372</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>20939130.4</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>18278584.3</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16711913.28</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>2660546</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>365285.7658711561</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>198452.8801595196</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>41.21</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>100.84</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>101.13</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>104.01</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>734.33</t>
-        </is>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-98.21</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>34139809.84533899</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>22233266</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>17863358.6</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16748608.22</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>4369907</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>395619.0178187264</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>923014.0142268091</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>5.37</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>9856</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>437.196</t>
+          <t>156.726</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.06</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>100.62</v>
+        <v>100.84</v>
       </c>
       <c r="AN8" t="n">
-        <v>101.15</v>
+        <v>101.13</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.98</t>
+          <t>104.01</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>963.68</t>
+          <t>734.33</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.49</t>
+          <t>-98.21</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>34139809.84533899</t>
+          <t>34125026.14104372</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>23791556.2</v>
+        <v>22233266</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18247321.0</t>
+          <t>17863358.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>16591916.72</v>
+        <v>16748608.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5544235</t>
+          <t>4369907</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>299729.0184718022</t>
+          <t>395619.0178187264</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1596608.812386263</t>
+          <t>923014.0142268091</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>104.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,34 +3837,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>437.196</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>104.253</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3987,47 +3987,47 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>101.9</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>100.4</v>
+        <v>100.62</v>
       </c>
       <c r="AN9" t="n">
-        <v>101.18</v>
+        <v>101.15</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.91</t>
+          <t>103.98</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>245.52</t>
+          <t>963.68</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.28</v>
+        <v>0.48</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.09</t>
+          <t>-101.49</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34139809.84533899</t>
+          <t>34125026.14104372</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>16409948</v>
+        <v>23791556.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15497425.0</t>
+          <t>18247321.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>16032717.96</v>
+        <v>16591916.72</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>912523</t>
+          <t>5544235</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>63932.69230553659</t>
+          <t>299729.0184718022</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-661503.6121140253</t>
+          <t>1596608.812386263</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>185.485</t>
+          <t>104.253</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4405,51 +4405,51 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.9</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>100.21</v>
+        <v>100.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>101.21</v>
+        <v>101.18</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.84</t>
+          <t>103.91</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>136.91</t>
+          <t>245.52</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.31</v>
+        <v>-0.19</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.22</t>
+          <t>-105.09</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34139809.84533899</t>
+          <t>34125026.14104372</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>17236697.2</v>
+        <v>16409948</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16837560.9</t>
+          <t>15497425.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>16046320.32</v>
+        <v>16032717.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>399136</t>
+          <t>912523</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>195830.2022000024</t>
+          <t>63932.69230553659</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-122124.6609675102</t>
+          <t>-661503.6121140253</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,17 +4634,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>192.142</t>
+          <t>185.485</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,12 +4812,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4827,51 +4827,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.7</v>
+        <v>1.19</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>100.06</v>
+        <v>100.21</v>
       </c>
       <c r="AN11" t="n">
-        <v>101.25</v>
+        <v>101.21</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.76</t>
+          <t>103.84</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>136.91</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.41</v>
+        <v>-0.31</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.03</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34139809.84533899</t>
+          <t>34125026.14104372</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>15618038.2</v>
+        <v>17236697.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17093791.3</t>
+          <t>16837560.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>16033026.32</v>
+        <v>16046320.32</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1475753</t>
+          <t>399136</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>253640.1773213683</t>
+          <t>195830.2022000024</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-228928.7785807922</t>
+          <t>-122124.6609675102</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>236.602</t>
+          <t>192.142</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.16</v>
+        <v>0.7</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>100.08</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>99.92</v>
+        <v>100.06</v>
       </c>
       <c r="AN12" t="n">
-        <v>101.31</v>
+        <v>101.25</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.76</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.26</v>
+        <v>-0.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.49</v>
+        <v>-0.41</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-113.14</t>
+          <t>-111.03</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34139809.84533899</t>
+          <t>34125026.14104372</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>13493451.2</v>
+        <v>15618038.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19986857.1</t>
+          <t>17093791.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>17696692.44</v>
+        <v>16033026.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-6493405</t>
+          <t>-1475753</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>341379.9874853975</t>
+          <t>253640.1773213683</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-434641.9187933095</t>
+          <t>-228928.7785807922</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>23951861.0</t>
+          <t>19564829.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>152.493</t>
+          <t>206.338</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-36.53</t>
+          <t>-22.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,38 +1014,38 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.87</v>
+        <v>0.39</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,26 +1054,26 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>101.72</v>
+        <v>101.82</v>
       </c>
       <c r="AN2" t="n">
-        <v>100.96</v>
+        <v>100.99</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.94</t>
+          <t>103.88</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-86.44</t>
+          <t>-85.32</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>34125026.14104372</t>
+          <t>34122386.30915493</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>15772109.0</t>
+          <t>21500497.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9733859</v>
+        <v>12100663.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>15336494.7</t>
+          <t>15587285.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>16314807.64</v>
+        <v>16017995.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5602635</t>
+          <t>-3486622</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-667551.5014074596</t>
+          <t>-667146.7991246434</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1451689.805058748</t>
+          <t>-664920.9365691543</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>15772109.0</t>
+          <t>21500497.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,42 +1305,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>152.493</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>82.876</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-41.47</t>
+          <t>-36.53</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.39</v>
+        <v>0.87</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>102.9</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>101.67</v>
+        <v>101.72</v>
       </c>
       <c r="AN3" t="n">
         <v>100.96</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>103.94</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-87.73</t>
+          <t>-86.44</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>34125026.14104372</t>
+          <t>34122386.30915493</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8468817.0</t>
+          <t>15772109.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9198267.4</v>
+        <v>9733859</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>15715766.7</t>
+          <t>15336494.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>16350764.5</v>
+        <v>16314807.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-6517499</t>
+          <t>-5602635</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-524980.9007435892</t>
+          <t>-667551.5014074596</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1910043.409863211</t>
+          <t>-1451689.805058748</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>8468817.0</t>
+          <t>15772109.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>74.992</t>
+          <t>82.876</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-37.81</t>
+          <t>-41.47</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,261 +1858,261 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>59.13</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.49</v>
+        <v>-0.39</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>102.9</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>104.03</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>34.25</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-87.73</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>34122386.30915493</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>8468817.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>9198267.4</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>15715766.7</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>16350764.5</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-6517499</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-524980.9007435892</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-1910043.409863211</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>8468817.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>9.42</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>41.33</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>9952</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="AM4" t="n">
-        <v>101.62</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>101.01</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>104.12</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>56.06</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-88.78</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>34125026.14104372</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>7689655.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>10736586</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>17264071.1</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16342819.74</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-6527485</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-273151.3536309307</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-1714122.866374472</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>7689655.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>-0.97</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>5.29</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>41.21</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>68.439</t>
+          <t>74.992</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>-37.81</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>59.13</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>101.44</v>
+        <v>101.62</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.05</v>
+        <v>101.01</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>104.11</t>
+          <t>104.12</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>92.57</t>
+          <t>56.06</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-90.35</t>
+          <t>-88.78</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>34125026.14104372</t>
+          <t>34122386.30915493</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>18335692.4</v>
+        <v>10736586</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17372820.2</t>
+          <t>17264071.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>16470596.92</v>
+        <v>16342819.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>962872</t>
+          <t>-6527485</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-11156.53313210487</t>
+          <t>-273151.3536309307</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1289536.059020042</t>
+          <t>-1714122.866374472</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>93.449</t>
+          <t>68.439</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.41</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,38 +2702,38 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.19</v>
+        <v>-0.29</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2742,26 +2742,26 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>101.26</v>
+        <v>101.44</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.09</v>
+        <v>101.05</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>104.08</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>146.84</t>
+          <t>92.57</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-92.58</t>
+          <t>-90.35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34125026.14104372</t>
+          <t>34122386.30915493</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>19073908.2</v>
+        <v>18335692.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18155302.7</t>
+          <t>17372820.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>16618262.3</v>
+        <v>16470596.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>918605</t>
+          <t>962872</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>221276.1079384292</t>
+          <t>-11156.53313210487</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-570777.0106915683</t>
+          <t>-1289536.059020042</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2886,17 +2886,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>103.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,34 +2993,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>93.449</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>126.465</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>82.54</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>101.08</v>
+        <v>101.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>101.11</v>
+        <v>101.09</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>104.05</t>
+          <t>104.08</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>247.67</t>
+          <t>146.84</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-92.58</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>34125026.14104372</t>
+          <t>34122386.30915493</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>20939130.4</v>
+        <v>19073908.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18278584.3</t>
+          <t>18155302.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>16711913.28</v>
+        <v>16618262.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2660546</t>
+          <t>918605</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>365285.7658711561</t>
+          <t>221276.1079384292</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>198452.8801595196</t>
+          <t>-570777.0106915683</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,14 +3368,14 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
           <t>103.0</t>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>156.726</t>
+          <t>126.465</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,261 +3546,261 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>92.06</t>
+          <t>82.54</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>104.05</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>247.67</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-95.31</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>34122386.30915493</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>20939130.4</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>18278584.3</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>16711913.28</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>2660546</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>365285.7658711561</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>198452.8801595196</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>9.42</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>41.33</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>9952</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>100.84</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>101.13</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>104.01</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>734.33</t>
-        </is>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-98.21</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>34125026.14104372</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>22233266</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>17863358.6</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>16748608.22</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>4369907</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>395619.0178187264</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>923014.0142268091</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>5.29</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>41.21</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>437.196</t>
+          <t>156.726</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.06</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>100.62</v>
+        <v>100.84</v>
       </c>
       <c r="AN9" t="n">
-        <v>101.15</v>
+        <v>101.13</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.98</t>
+          <t>104.01</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>963.68</t>
+          <t>734.33</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.49</t>
+          <t>-98.21</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>34125026.14104372</t>
+          <t>34122386.30915493</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>23791556.2</v>
+        <v>22233266</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18247321.0</t>
+          <t>17863358.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>16591916.72</v>
+        <v>16748608.22</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5544235</t>
+          <t>4369907</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>299729.0184718022</t>
+          <t>395619.0178187264</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1596608.812386263</t>
+          <t>923014.0142268091</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>104.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,42 +4259,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>437.196</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>104.253</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4409,47 +4409,47 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>101.9</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>100.4</v>
+        <v>100.62</v>
       </c>
       <c r="AN10" t="n">
-        <v>101.18</v>
+        <v>101.15</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.91</t>
+          <t>103.98</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>245.52</t>
+          <t>963.68</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.28</v>
+        <v>0.48</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.09</t>
+          <t>-101.49</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34125026.14104372</t>
+          <t>34122386.30915493</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>16409948</v>
+        <v>23791556.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15497425.0</t>
+          <t>18247321.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>16032717.96</v>
+        <v>16591916.72</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>912523</t>
+          <t>5544235</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>63932.69230553659</t>
+          <t>299729.0184718022</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-661503.6121140253</t>
+          <t>1596608.812386263</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>185.485</t>
+          <t>104.253</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,12 +4812,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4827,51 +4827,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>100.21</v>
+        <v>100.4</v>
       </c>
       <c r="AN11" t="n">
-        <v>101.21</v>
+        <v>101.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>103.84</t>
+          <t>103.91</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>136.91</t>
+          <t>245.52</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.31</v>
+        <v>-0.19</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.22</t>
+          <t>-105.09</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34125026.14104372</t>
+          <t>34122386.30915493</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>17236697.2</v>
+        <v>16409948</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>16837560.9</t>
+          <t>15497425.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>16046320.32</v>
+        <v>16032717.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>399136</t>
+          <t>912523</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>195830.2022000024</t>
+          <t>63932.69230553659</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-122124.6609675102</t>
+          <t>-661503.6121140253</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>18992585.0</t>
+          <t>10763319.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,17 +5056,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>192.142</t>
+          <t>185.485</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5249,51 +5249,51 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.7</v>
+        <v>1.19</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>100.06</v>
+        <v>100.21</v>
       </c>
       <c r="AN12" t="n">
-        <v>101.25</v>
+        <v>101.21</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>103.76</t>
+          <t>103.84</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>136.91</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.41</v>
+        <v>-0.31</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.03</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>34125026.14104372</t>
+          <t>34122386.30915493</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>15618038.2</v>
+        <v>17236697.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17093791.3</t>
+          <t>16837560.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>16033026.32</v>
+        <v>16046320.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1475753</t>
+          <t>399136</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>253640.1773213683</t>
+          <t>195830.2022000024</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-228928.7785807922</t>
+          <t>-122124.6609675102</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>19564829.0</t>
+          <t>18992585.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -923,167 +923,167 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>185.25</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>133.509</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-7.96</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2025/07/01</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-15.33</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-8.41</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>2025/07/01</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,17 +1094,17 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1113,47 +1113,47 @@
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>0.29</v>
+        <v>0.48</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>101.97</v>
+        <v>102.17</v>
       </c>
       <c r="AV2" t="n">
-        <v>101</v>
+        <v>101.03</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>103.71</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-84.40</t>
+          <t>-83.47</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>34103666.60126583</t>
+          <t>34096321.48735955</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>13875116.0</t>
+          <t>19249297.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>13461238.8</v>
+        <v>15773167.2</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>15898465.6</t>
+          <t>13254876.6</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>16058200.18</v>
+        <v>16058446.28</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-2437226</t>
+          <t>2518290</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-667503.1808304227</t>
+          <t>-603709.270511441</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-669463.2802122086</t>
+          <t>-252842.7637570426</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>13875116.0</t>
+          <t>19249297.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,167 +1385,167 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>133.509</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-15.33</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-8.41</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2025/07/01</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>6.63</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>-0.48</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>206.338</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-22.37</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-8.41</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>2025/07/01</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-1.45</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,12 +1556,12 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1571,51 +1571,51 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>103.1</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>101.82</v>
+        <v>101.97</v>
       </c>
       <c r="AV3" t="n">
-        <v>100.99</v>
+        <v>101</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>103.88</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-85.32</t>
+          <t>-84.40</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>34103666.60126583</t>
+          <t>34096321.48735955</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>21500497.0</t>
+          <t>13875116.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>12100663.6</v>
+        <v>13461238.8</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>15587285.9</t>
+          <t>15898465.6</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>16017995.62</v>
+        <v>16058200.18</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-3486622</t>
+          <t>-2437226</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-667146.7991246434</t>
+          <t>-667503.1808304227</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-664920.9365691543</t>
+          <t>-669463.2802122086</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>21500497.0</t>
+          <t>13875116.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>152.493</t>
+          <t>206.338</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-36.53</t>
+          <t>-22.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,38 +2018,38 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>0.87</v>
+        <v>0.39</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
@@ -2058,26 +2058,26 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>101.72</v>
+        <v>101.82</v>
       </c>
       <c r="AV4" t="n">
-        <v>100.96</v>
+        <v>100.99</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>103.94</t>
+          <t>103.88</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-86.44</t>
+          <t>-85.32</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>34103666.60126583</t>
+          <t>34096321.48735955</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>15772109.0</t>
+          <t>21500497.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>9733859</v>
+        <v>12100663.6</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>15336494.7</t>
+          <t>15587285.9</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>16314807.64</v>
+        <v>16017995.62</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-5602635</t>
+          <t>-3486622</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-667551.5014074596</t>
+          <t>-667146.7991246434</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-1451689.805058748</t>
+          <t>-664920.9365691543</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>15772109.0</t>
+          <t>21500497.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,34 +2309,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>152.493</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>82.876</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-41.47</t>
+          <t>-36.53</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,66 +2480,66 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>-0.39</v>
+        <v>0.87</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>102.9</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>101.67</v>
+        <v>101.72</v>
       </c>
       <c r="AV5" t="n">
         <v>100.96</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>103.94</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-87.73</t>
+          <t>-86.44</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>34103666.60126583</t>
+          <t>34096321.48735955</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>8468817.0</t>
+          <t>15772109.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>9198267.4</v>
+        <v>9733859</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>15715766.7</t>
+          <t>15336494.7</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>16350764.5</v>
+        <v>16314807.64</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-6517499</t>
+          <t>-5602635</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-524980.9007435892</t>
+          <t>-667551.5014074596</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-1910043.409863211</t>
+          <t>-1451689.805058748</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>8468817.0</t>
+          <t>15772109.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2659,22 +2659,22 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>74.992</t>
+          <t>82.876</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-37.81</t>
+          <t>-41.47</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,261 +2942,261 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>59.13</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>-0.49</v>
+        <v>-0.39</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>102.9</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>104.03</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>34.25</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-87.73</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>34096321.48735955</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>8468817.0</t>
+        </is>
+      </c>
+      <c r="BF6" t="n">
+        <v>9198267.4</v>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>15715766.7</t>
+        </is>
+      </c>
+      <c r="BH6" t="n">
+        <v>16350764.5</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-6517499</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>-524980.9007435892</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>-1910043.409863211</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>8468817.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>41.03</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="AU6" t="n">
-        <v>101.62</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>101.01</v>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>104.12</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>56.06</t>
-        </is>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-88.78</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>34103666.60126583</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>7689655.0</t>
-        </is>
-      </c>
-      <c r="BF6" t="n">
-        <v>10736586</v>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>17264071.1</t>
-        </is>
-      </c>
-      <c r="BH6" t="n">
-        <v>16342819.74</v>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>-6527485</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>-273151.3536309307</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>-1714122.866374472</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>7689655.0</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>-0.97</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>9.42</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>41.09</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
-        <is>
-          <t>9952</t>
-        </is>
-      </c>
-      <c r="CI6" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CJ6" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CK6" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>68.439</t>
+          <t>74.992</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>-37.81</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,66 +3404,66 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>59.13</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>101.44</v>
+        <v>101.62</v>
       </c>
       <c r="AV7" t="n">
-        <v>101.05</v>
+        <v>101.01</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>104.11</t>
+          <t>104.12</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>92.57</t>
+          <t>56.06</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-90.35</t>
+          <t>-88.78</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>34103666.60126583</t>
+          <t>34096321.48735955</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>18335692.4</v>
+        <v>10736586</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>17372820.2</t>
+          <t>17264071.1</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>16470596.92</v>
+        <v>16342819.74</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>962872</t>
+          <t>-6527485</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-11156.53313210487</t>
+          <t>-273151.3536309307</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-1289536.059020042</t>
+          <t>-1714122.866374472</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>93.449</t>
+          <t>68.439</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.41</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,38 +3866,38 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>0.19</v>
+        <v>-0.29</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
@@ -3906,26 +3906,26 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>101.26</v>
+        <v>101.44</v>
       </c>
       <c r="AV8" t="n">
-        <v>101.09</v>
+        <v>101.05</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>104.08</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>146.84</t>
+          <t>92.57</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-92.58</t>
+          <t>-90.35</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>34103666.60126583</t>
+          <t>34096321.48735955</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>19073908.2</v>
+        <v>18335692.4</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>18155302.7</t>
+          <t>17372820.2</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>16618262.3</v>
+        <v>16470596.92</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>918605</t>
+          <t>962872</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>221276.1079384292</t>
+          <t>-11156.53313210487</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-570777.0106915683</t>
+          <t>-1289536.059020042</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4050,17 +4050,17 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CO8" t="inlineStr">
-        <is>
-          <t>103.5</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4147,7 +4147,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4157,42 +4157,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>93.449</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>126.465</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,66 +4328,66 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>82.54</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>101.08</v>
+        <v>101.26</v>
       </c>
       <c r="AV9" t="n">
-        <v>101.11</v>
+        <v>101.09</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>104.05</t>
+          <t>104.08</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>247.67</t>
+          <t>146.84</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-92.58</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>34103666.60126583</t>
+          <t>34096321.48735955</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>20939130.4</v>
+        <v>19073908.2</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>18278584.3</t>
+          <t>18155302.7</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>16711913.28</v>
+        <v>16618262.3</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>2660546</t>
+          <t>918605</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>365285.7658711561</t>
+          <t>221276.1079384292</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>198452.8801595196</t>
+          <t>-570777.0106915683</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4507,22 +4507,22 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,14 +4572,14 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
       <c r="CN9" t="inlineStr">
         <is>
           <t>103.0</t>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>156.726</t>
+          <t>126.465</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,261 +4790,261 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>92.06</t>
+          <t>82.54</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>104.05</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>247.67</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-95.31</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>34096321.48735955</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>20939130.4</v>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>18278584.3</t>
+        </is>
+      </c>
+      <c r="BH10" t="n">
+        <v>16711913.28</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>2660546</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>365285.7658711561</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>198452.8801595196</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>41.03</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="AU10" t="n">
-        <v>100.84</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>101.13</v>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>104.01</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>734.33</t>
-        </is>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-98.21</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>34103666.60126583</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BF10" t="n">
-        <v>22233266</v>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>17863358.6</t>
-        </is>
-      </c>
-      <c r="BH10" t="n">
-        <v>16748608.22</v>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>4369907</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>395619.0178187264</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>923014.0142268091</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>9.42</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>41.09</t>
-        </is>
-      </c>
-      <c r="CH10" t="inlineStr">
-        <is>
-          <t>9952</t>
-        </is>
-      </c>
-      <c r="CI10" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CJ10" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CK10" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CL10" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CM10" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CN10" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>437.196</t>
+          <t>156.726</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,142 +5106,142 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>24.46</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-8.85</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2025/07/01</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>7.79</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>-0.48</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>30.38</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-7.96</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>2025/07/01</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>21.72</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>0.02</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.06</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>100.62</v>
+        <v>100.84</v>
       </c>
       <c r="AV11" t="n">
-        <v>101.15</v>
+        <v>101.13</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>103.98</t>
+          <t>104.01</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>963.68</t>
+          <t>734.33</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-101.49</t>
+          <t>-98.21</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>34103666.60126583</t>
+          <t>34096321.48735955</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>23791556.2</v>
+        <v>22233266</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>18247321.0</t>
+          <t>17863358.6</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>16591916.72</v>
+        <v>16748608.22</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>5544235</t>
+          <t>4369907</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>299729.0184718022</t>
+          <t>395619.0178187264</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>1596608.812386263</t>
+          <t>923014.0142268091</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CM11" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CN11" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="CO11" t="inlineStr">
-        <is>
-          <t>104.0</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,34 +5543,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>437.196</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>104.253</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,12 +5714,12 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5733,47 +5733,47 @@
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>101.9</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>100.4</v>
+        <v>100.62</v>
       </c>
       <c r="AV12" t="n">
-        <v>101.18</v>
+        <v>101.15</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>103.91</t>
+          <t>103.98</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>245.52</t>
+          <t>963.68</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>0.28</v>
+        <v>0.48</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-105.09</t>
+          <t>-101.49</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>34103666.60126583</t>
+          <t>34096321.48735955</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>16409948</v>
+        <v>23791556.2</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>15497425.0</t>
+          <t>18247321.0</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>16032717.96</v>
+        <v>16591916.72</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>912523</t>
+          <t>5544235</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>63932.69230553659</t>
+          <t>299729.0184718022</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-661503.6121140253</t>
+          <t>1596608.812386263</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>10763319.0</t>
+          <t>45685187.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/10/03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>101.5</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>98.5</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>9.20</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>77.78</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>0.48</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-2.58</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>102.17</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>101.03</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>103.71</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>22.49</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>0.75</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>0.61</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-83.47</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>34096321.48735955</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>19249297.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>15773167.2</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>13254876.6</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>16058446.28</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>2518290</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-603709.270511441</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-252842.7637570426</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>19249297.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>9.46</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/10/03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>101.5</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>98.5</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>6.63</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-0.48</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>77.78</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>0.29</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>1.21</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-2.69</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>103.2</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>101.97</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>101</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>103.8</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>23.63</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>0.72</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>0.58</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-84.40</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>34096321.48735955</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>13875116.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>13461238.8</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>15898465.6</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>16058200.18</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>-2437226</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-667503.1808304227</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-669463.2802122086</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>13875116.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>9.46</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/10/03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>101.5</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>98.5</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>10.25</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-1.45</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>55.56</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>0.39</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>1.26</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-2.78</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>103.1</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>101.82</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>100.99</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>103.88</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>30.47</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>0.71</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>0.55</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-85.32</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>34096321.48735955</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>21500497.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>12100663.6</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>15587285.9</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>16017995.62</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-3486622</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-667146.7991246434</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-664920.9365691543</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>21500497.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>9.46</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>105.0</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>105.0</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/10/03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>101.5</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>98.5</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>7.58</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>1.96</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>41.67</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>0.87</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>1.36</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-2.87</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>103.1</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>101.72</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>100.96</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>103.94</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>37.89</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>0.7</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>0.5</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-86.44</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>34096321.48735955</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>15772109.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>9733859</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>15336494.7</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>16314807.64</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>-5602635</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-667551.5014074596</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-1451689.805058748</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>15772109.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>9.46</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>102.0</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>102.0</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/10/03</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>101.5</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>98.5</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>4.12</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>30.56</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>-0.39</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>1.21</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-2.95</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>102.9</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>101.67</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>100.96</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>104.03</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>34.25</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>0.61</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>0.46</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-87.73</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>34096321.48735955</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>8468817.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>9198267.4</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>15715766.7</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>16350764.5</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-6517499</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-524980.9007435892</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-1910043.409863211</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>8468817.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-0.97</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>9.46</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>101.5</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/10/03</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>101.5</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>98.5</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>3.73</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>59.13</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>-0.49</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>1.36</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-2.99</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>101.62</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>101.01</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>104.12</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>56.06</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>0.65</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>0.42</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-88.78</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>34096321.48735955</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>7689655.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>10736586</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>17264071.1</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>16342819.74</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-6527485</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-273151.3536309307</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-1714122.866374472</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>7689655.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-0.97</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>9.46</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>102.0</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/10/03</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>101.5</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>98.5</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>-0.97</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>74.6</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>1.83</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-2.94</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>103.3</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>101.44</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>101.05</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>104.11</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>92.57</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>0.36</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-90.35</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>34096321.48735955</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>7072240.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>18335692.4</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>17372820.2</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>16470596.92</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>962872</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-11156.53313210487</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-1289536.059020042</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>7072240.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-0.48</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>9.46</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/10/03</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>101.5</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>98.5</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>4.64</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>85.71</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>77.78</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>0.19</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>2.01</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>0.17</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-2.87</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>103.3</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>101.26</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>101.09</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>104.08</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>146.84</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>0.68</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>0.28</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-92.58</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>34096321.48735955</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>9666474.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>19073908.2</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>18155302.7</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>16618262.3</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>918605</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>221276.1079384292</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-570777.0106915683</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>9666474.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>9.46</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/10/03</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>101.5</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>98.5</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>6.28</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-0.97</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>71.43</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>82.54</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>2.09</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-0.03</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-2.82</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>103.2</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>101.08</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>101.11</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>247.67</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>0.61</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>0.17</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-95.31</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>34096321.48735955</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>13094151.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>20939130.4</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>18278584.3</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>16711913.28</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>2660546</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>365285.7658711561</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>198452.8801595196</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>13094151.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-0.48</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>9.46</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/10/03</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>101.5</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>98.5</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>7.79</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-0.48</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>76.19</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>92.06</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>2.14</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-0.28</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-2.77</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>100.84</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>101.13</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>104.01</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>734.33</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>0.55</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-98.21</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>34096321.48735955</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>16160410.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>22233266</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>17863358.6</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>16748608.22</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>4369907</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>395619.0178187264</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>923014.0142268091</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>16160410.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-0.48</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>9.46</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/10/03</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>101.5</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>98.5</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>21.72</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>1.36</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>1.96</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-0.52</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>-2.72</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>102.6</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>100.62</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>101.15</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>103.98</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>963.68</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>0.48</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-101.49</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>34096321.48735955</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>45685187.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>23791556.2</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>18247321.0</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>16591916.72</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>5544235</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>299729.0184718022</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>1596608.812386263</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>45685187.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>巨路</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>0.7848146795386409</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-28.78483981056313</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>-7.753976956109076</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>9.46</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>32.64%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>15.64%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>程式控制86.38%、電子13.62% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>巨路-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>105.5</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>75.01</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 半導體 - IC通路** 平面顯示器 - 其他零組件** 通信網路 - 線材** 其他 - 其他** 汽電共生 - 系統整合、設備維護</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>185.25</t>
+          <t>131.916</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1153,247 +1153,247 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.48</v>
+        <v>-0.19</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>103.7</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>102.42</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>101.07</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>103.64</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>14.76</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>-82.84</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>34077251.36886396</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>13666218.0</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>16812647.4</v>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>13005457.4</t>
+        </is>
+      </c>
+      <c r="BL2" t="n">
+        <v>16188996.48</v>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>3807189</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-568310.6532242196</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-373618.2581445016</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>13666218.0</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>102.17</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>101.03</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>103.71</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>22.49</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>-83.47</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>34096321.48735955</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>19249297.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>15773167.2</v>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>13254876.6</t>
-        </is>
-      </c>
-      <c r="BL2" t="n">
-        <v>16058446.28</v>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>2518290</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-603709.270511441</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-252842.7637570426</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>19249297.0</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>9.42</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>40.95</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>9952</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
         <is>
           <t>103.5</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>5.29</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>41.03</t>
-        </is>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>104.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,187 +1425,187 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>185.25</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>133.509</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-7.96</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-15.33</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/07/01</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>113.0</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-8.41</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/07/01</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,17 +1616,17 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1635,47 +1635,47 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.29</v>
+        <v>0.48</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>101.97</v>
+        <v>102.17</v>
       </c>
       <c r="AZ3" t="n">
-        <v>101</v>
+        <v>101.03</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>103.71</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-84.40</t>
+          <t>-83.47</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>34096321.48735955</t>
+          <t>34077251.36886396</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>13875116.0</t>
+          <t>19249297.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>13461238.8</v>
+        <v>15773167.2</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>15898465.6</t>
+          <t>13254876.6</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>16058200.18</v>
+        <v>16058446.28</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-2437226</t>
+          <t>2518290</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-667503.1808304227</t>
+          <t>-603709.270511441</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-669463.2802122086</t>
+          <t>-252842.7637570426</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>13875116.0</t>
+          <t>19249297.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,187 +1907,187 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>133.509</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-15.33</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-8.41</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/07/01</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>6.63</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
           <t>-0.48</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>206.338</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-22.37</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-8.41</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/07/01</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>-1.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,12 +2098,12 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>103.1</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>101.82</v>
+        <v>101.97</v>
       </c>
       <c r="AZ4" t="n">
-        <v>100.99</v>
+        <v>101</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>103.88</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-85.32</t>
+          <t>-84.40</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>34096321.48735955</t>
+          <t>34077251.36886396</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>21500497.0</t>
+          <t>13875116.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>12100663.6</v>
+        <v>13461238.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>15587285.9</t>
+          <t>15898465.6</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>16017995.62</v>
+        <v>16058200.18</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-3486622</t>
+          <t>-2437226</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-667146.7991246434</t>
+          <t>-667503.1808304227</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-664920.9365691543</t>
+          <t>-669463.2802122086</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>21500497.0</t>
+          <t>13875116.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>152.493</t>
+          <t>206.338</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-36.53</t>
+          <t>-22.37</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,38 +2580,38 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.87</v>
+        <v>0.39</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2620,26 +2620,26 @@
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>101.72</v>
+        <v>101.82</v>
       </c>
       <c r="AZ5" t="n">
-        <v>100.96</v>
+        <v>100.99</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>103.94</t>
+          <t>103.88</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-86.44</t>
+          <t>-85.32</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>34096321.48735955</t>
+          <t>34077251.36886396</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>15772109.0</t>
+          <t>21500497.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>9733859</v>
+        <v>12100663.6</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>15336494.7</t>
+          <t>15587285.9</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>16314807.64</v>
+        <v>16017995.62</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-5602635</t>
+          <t>-3486622</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-667551.5014074596</t>
+          <t>-667146.7991246434</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1451689.805058748</t>
+          <t>-664920.9365691543</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>15772109.0</t>
+          <t>21500497.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,42 +2871,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>152.493</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>82.876</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-41.47</t>
+          <t>-36.53</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.39</v>
+        <v>0.87</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>102.9</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>101.67</v>
+        <v>101.72</v>
       </c>
       <c r="AZ6" t="n">
         <v>100.96</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>103.94</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-87.73</t>
+          <t>-86.44</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>34096321.48735955</t>
+          <t>34077251.36886396</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>8468817.0</t>
+          <t>15772109.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>9198267.4</v>
+        <v>9733859</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>15715766.7</t>
+          <t>15336494.7</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>16350764.5</v>
+        <v>16314807.64</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-6517499</t>
+          <t>-5602635</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-524980.9007435892</t>
+          <t>-667551.5014074596</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1910043.409863211</t>
+          <t>-1451689.805058748</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>8468817.0</t>
+          <t>15772109.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>74.992</t>
+          <t>82.876</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-37.81</t>
+          <t>-41.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,261 +3544,261 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>59.13</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.49</v>
+        <v>-0.39</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
+          <t>102.9</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>104.03</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>34.25</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>-87.73</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>34077251.36886396</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>8468817.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>9198267.4</v>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>15715766.7</t>
+        </is>
+      </c>
+      <c r="BL7" t="n">
+        <v>16350764.5</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>-6517499</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-524980.9007435892</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-1910043.409863211</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>8468817.0</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>9.42</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>40.95</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>9952</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="AY7" t="n">
-        <v>101.62</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>101.01</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>104.12</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>56.06</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>-88.78</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>34096321.48735955</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>7689655.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="n">
-        <v>10736586</v>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>17264071.1</t>
-        </is>
-      </c>
-      <c r="BL7" t="n">
-        <v>16342819.74</v>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>-6527485</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-273151.3536309307</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-1714122.866374472</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>7689655.0</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>-0.97</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>5.29</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="CH7" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
-      <c r="CI7" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="CJ7" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="CK7" t="inlineStr">
-        <is>
-          <t>41.03</t>
-        </is>
-      </c>
-      <c r="CL7" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="CM7" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN7" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CO7" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CP7" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="CQ7" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>68.439</t>
+          <t>74.992</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>-37.81</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>59.13</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>101.44</v>
+        <v>101.62</v>
       </c>
       <c r="AZ8" t="n">
-        <v>101.05</v>
+        <v>101.01</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>104.11</t>
+          <t>104.12</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>92.57</t>
+          <t>56.06</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-90.35</t>
+          <t>-88.78</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>34096321.48735955</t>
+          <t>34077251.36886396</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>18335692.4</v>
+        <v>10736586</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>17372820.2</t>
+          <t>17264071.1</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>16470596.92</v>
+        <v>16342819.74</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>962872</t>
+          <t>-6527485</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-11156.53313210487</t>
+          <t>-273151.3536309307</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-1289536.059020042</t>
+          <t>-1714122.866374472</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>93.449</t>
+          <t>68.439</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.41</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,38 +4508,38 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.19</v>
+        <v>-0.29</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4548,26 +4548,26 @@
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>101.26</v>
+        <v>101.44</v>
       </c>
       <c r="AZ9" t="n">
-        <v>101.09</v>
+        <v>101.05</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>104.08</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>146.84</t>
+          <t>92.57</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-92.58</t>
+          <t>-90.35</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>34096321.48735955</t>
+          <t>34077251.36886396</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>19073908.2</v>
+        <v>18335692.4</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>18155302.7</t>
+          <t>17372820.2</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>16618262.3</v>
+        <v>16470596.92</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>918605</t>
+          <t>962872</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>221276.1079384292</t>
+          <t>-11156.53313210487</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-570777.0106915683</t>
+          <t>-1289536.059020042</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4692,17 +4692,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CS9" t="inlineStr">
-        <is>
-          <t>103.5</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4789,7 +4789,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4799,34 +4799,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>93.449</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>126.465</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>82.54</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>101.08</v>
+        <v>101.26</v>
       </c>
       <c r="AZ10" t="n">
-        <v>101.11</v>
+        <v>101.09</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>104.05</t>
+          <t>104.08</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>247.67</t>
+          <t>146.84</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-92.58</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>34096321.48735955</t>
+          <t>34077251.36886396</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>20939130.4</v>
+        <v>19073908.2</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>18278584.3</t>
+          <t>18155302.7</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>16711913.28</v>
+        <v>16618262.3</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>2660546</t>
+          <t>918605</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>365285.7658711561</t>
+          <t>221276.1079384292</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>198452.8801595196</t>
+          <t>-570777.0106915683</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
       <c r="CR10" t="inlineStr">
         <is>
           <t>103.0</t>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>156.726</t>
+          <t>126.465</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,261 +5472,261 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>92.06</t>
+          <t>82.54</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>104.05</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>247.67</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>-95.31</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>34077251.36886396</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>20939130.4</v>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>18278584.3</t>
+        </is>
+      </c>
+      <c r="BL11" t="n">
+        <v>16711913.28</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>2660546</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>365285.7658711561</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>198452.8801595196</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>9.42</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>40.95</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>9952</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="AY11" t="n">
-        <v>100.84</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>101.13</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>104.01</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>734.33</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>-98.21</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>34096321.48735955</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BJ11" t="n">
-        <v>22233266</v>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>17863358.6</t>
-        </is>
-      </c>
-      <c r="BL11" t="n">
-        <v>16748608.22</v>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>4369907</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>395619.0178187264</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>923014.0142268091</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>5.29</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
-      <c r="CI11" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="CJ11" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="CK11" t="inlineStr">
-        <is>
-          <t>41.03</t>
-        </is>
-      </c>
-      <c r="CL11" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="CM11" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN11" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CO11" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CP11" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CQ11" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>437.196</t>
+          <t>156.726</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.06</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>100.62</v>
+        <v>100.84</v>
       </c>
       <c r="AZ12" t="n">
-        <v>101.15</v>
+        <v>101.13</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>103.98</t>
+          <t>104.01</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>963.68</t>
+          <t>734.33</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-101.49</t>
+          <t>-98.21</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>34096321.48735955</t>
+          <t>34077251.36886396</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>23791556.2</v>
+        <v>22233266</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>18247321.0</t>
+          <t>17863358.6</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>16591916.72</v>
+        <v>16748608.22</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>5544235</t>
+          <t>4369907</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>299729.0184718022</t>
+          <t>395619.0178187264</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>1596608.812386263</t>
+          <t>923014.0142268091</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>45685187.0</t>
+          <t>16160410.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CS12" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CQ12" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="CS12" t="inlineStr">
-        <is>
-          <t>104.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -948,7 +948,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>131.916</t>
+          <t>140.395</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.41</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,63 +1134,63 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>77.78</t>
-        </is>
-      </c>
       <c r="AT2" t="n">
-        <v>-0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.25</v>
+        <v>0.84</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>103.7</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>102.42</v>
+        <v>102.64</v>
       </c>
       <c r="AZ2" t="n">
-        <v>101.07</v>
+        <v>101.1</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>103.54</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BD2" t="n">
         <v>0.64</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-82.84</t>
+          <t>-82.68</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>34077251.36886396</t>
+          <t>34060096.23319328</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>13666218.0</t>
+          <t>14552323.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>16812647.4</v>
+        <v>16568690.2</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>13005457.4</t>
+          <t>13151274.6</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>16188996.48</v>
+        <v>16279672.76</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>3807189</t>
+          <t>3417415</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-568310.6532242196</t>
+          <t>-539703.2869992794</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-373618.2581445016</t>
+          <t>-382362.7727621086</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>13666218.0</t>
+          <t>14552323.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>185.25</t>
+          <t>131.916</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,162 +1450,162 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>29.27</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-8.41</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/07/01</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>6.55</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
           <t>-0.48</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-7.96</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/07/01</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>9.20</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,17 +1616,17 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1635,247 +1635,247 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.48</v>
+        <v>-0.19</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>103.7</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>102.42</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>101.07</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>103.64</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>14.76</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>-82.84</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>34060096.23319328</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>13666218.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="n">
+        <v>16812647.4</v>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>13005457.4</t>
+        </is>
+      </c>
+      <c r="BL3" t="n">
+        <v>16188996.48</v>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>3807189</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-568310.6532242196</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-373618.2581445016</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>13666218.0</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="AY3" t="n">
-        <v>102.17</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>101.03</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>103.71</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>22.49</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>-83.47</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>34077251.36886396</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>19249297.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="n">
-        <v>15773167.2</v>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>13254876.6</t>
-        </is>
-      </c>
-      <c r="BL3" t="n">
-        <v>16058446.28</v>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>2518290</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-603709.270511441</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-252842.7637570426</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>19249297.0</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>40.56</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
         <is>
           <t>103.5</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>9.42</t>
-        </is>
-      </c>
-      <c r="CI3" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="CJ3" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="CK3" t="inlineStr">
-        <is>
-          <t>40.95</t>
-        </is>
-      </c>
-      <c r="CL3" t="inlineStr">
-        <is>
-          <t>9952</t>
-        </is>
-      </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CP3" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>104.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,187 +1907,187 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>185.25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>133.509</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-7.96</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-15.33</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/07/01</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>113.0</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-8.41</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/07/01</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,17 +2098,17 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2117,47 +2117,47 @@
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0.29</v>
+        <v>0.48</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>101.97</v>
+        <v>102.17</v>
       </c>
       <c r="AZ4" t="n">
-        <v>101</v>
+        <v>101.03</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>103.71</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-84.40</t>
+          <t>-83.47</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>34077251.36886396</t>
+          <t>34060096.23319328</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>13875116.0</t>
+          <t>19249297.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>13461238.8</v>
+        <v>15773167.2</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>15898465.6</t>
+          <t>13254876.6</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>16058200.18</v>
+        <v>16058446.28</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-2437226</t>
+          <t>2518290</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-667503.1808304227</t>
+          <t>-603709.270511441</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-669463.2802122086</t>
+          <t>-252842.7637570426</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>13875116.0</t>
+          <t>19249297.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,187 +2389,187 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>133.509</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-15.33</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-8.41</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/07/01</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>6.63</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
           <t>-0.48</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>206.338</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-22.37</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-8.41</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/07/01</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>113.0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>-1.45</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2595,51 +2595,51 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>103.1</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>101.82</v>
+        <v>101.97</v>
       </c>
       <c r="AZ5" t="n">
-        <v>100.99</v>
+        <v>101</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>103.88</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-85.32</t>
+          <t>-84.40</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>34077251.36886396</t>
+          <t>34060096.23319328</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>21500497.0</t>
+          <t>13875116.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>12100663.6</v>
+        <v>13461238.8</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>15587285.9</t>
+          <t>15898465.6</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>16017995.62</v>
+        <v>16058200.18</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-3486622</t>
+          <t>-2437226</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-667146.7991246434</t>
+          <t>-667503.1808304227</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-664920.9365691543</t>
+          <t>-669463.2802122086</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>21500497.0</t>
+          <t>13875116.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,17 +2824,17 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>152.493</t>
+          <t>206.338</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-36.53</t>
+          <t>-22.37</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,38 +3062,38 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.87</v>
+        <v>0.39</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -3102,26 +3102,26 @@
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>101.72</v>
+        <v>101.82</v>
       </c>
       <c r="AZ6" t="n">
-        <v>100.96</v>
+        <v>100.99</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>103.94</t>
+          <t>103.88</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-86.44</t>
+          <t>-85.32</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>34077251.36886396</t>
+          <t>34060096.23319328</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>15772109.0</t>
+          <t>21500497.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>9733859</v>
+        <v>12100663.6</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>15336494.7</t>
+          <t>15587285.9</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>16314807.64</v>
+        <v>16017995.62</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-5602635</t>
+          <t>-3486622</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-667551.5014074596</t>
+          <t>-667146.7991246434</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1451689.805058748</t>
+          <t>-664920.9365691543</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>15772109.0</t>
+          <t>21500497.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,42 +3353,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>152.493</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>82.876</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-41.47</t>
+          <t>-36.53</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.39</v>
+        <v>0.87</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>102.9</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>101.67</v>
+        <v>101.72</v>
       </c>
       <c r="AZ7" t="n">
         <v>100.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>103.94</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-87.73</t>
+          <t>-86.44</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>34077251.36886396</t>
+          <t>34060096.23319328</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>8468817.0</t>
+          <t>15772109.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>9198267.4</v>
+        <v>9733859</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>15715766.7</t>
+          <t>15336494.7</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>16350764.5</v>
+        <v>16314807.64</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-6517499</t>
+          <t>-5602635</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-524980.9007435892</t>
+          <t>-667551.5014074596</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1910043.409863211</t>
+          <t>-1451689.805058748</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>8468817.0</t>
+          <t>15772109.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,22 +3723,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>74.992</t>
+          <t>82.876</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-37.81</t>
+          <t>-41.47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,261 +4026,261 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>59.13</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.49</v>
+        <v>-0.39</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
+          <t>102.9</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>104.03</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>34.25</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>-87.73</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>34060096.23319328</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>8468817.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9198267.4</v>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>15715766.7</t>
+        </is>
+      </c>
+      <c r="BL8" t="n">
+        <v>16350764.5</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>-6517499</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-524980.9007435892</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-1910043.409863211</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>8468817.0</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>40.56</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="AY8" t="n">
-        <v>101.62</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>101.01</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>104.12</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>56.06</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>-88.78</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>34077251.36886396</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>7689655.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10736586</v>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>17264071.1</t>
-        </is>
-      </c>
-      <c r="BL8" t="n">
-        <v>16342819.74</v>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-6527485</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-273151.3536309307</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-1714122.866374472</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>7689655.0</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>-0.97</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr">
-        <is>
-          <t>9.42</t>
-        </is>
-      </c>
-      <c r="CI8" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="CJ8" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="CK8" t="inlineStr">
-        <is>
-          <t>40.95</t>
-        </is>
-      </c>
-      <c r="CL8" t="inlineStr">
-        <is>
-          <t>9952</t>
-        </is>
-      </c>
-      <c r="CM8" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN8" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CO8" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CP8" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="CQ8" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>68.439</t>
+          <t>74.992</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>-37.81</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>59.13</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>101.44</v>
+        <v>101.62</v>
       </c>
       <c r="AZ9" t="n">
-        <v>101.05</v>
+        <v>101.01</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>104.11</t>
+          <t>104.12</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>92.57</t>
+          <t>56.06</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-90.35</t>
+          <t>-88.78</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>34077251.36886396</t>
+          <t>34060096.23319328</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>18335692.4</v>
+        <v>10736586</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>17372820.2</t>
+          <t>17264071.1</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>16470596.92</v>
+        <v>16342819.74</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>962872</t>
+          <t>-6527485</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-11156.53313210487</t>
+          <t>-273151.3536309307</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-1289536.059020042</t>
+          <t>-1714122.866374472</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>7072240.0</t>
+          <t>7689655.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>93.449</t>
+          <t>68.439</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.41</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,38 +4990,38 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.19</v>
+        <v>-0.29</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -5030,26 +5030,26 @@
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>101.26</v>
+        <v>101.44</v>
       </c>
       <c r="AZ10" t="n">
-        <v>101.09</v>
+        <v>101.05</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>104.08</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>146.84</t>
+          <t>92.57</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-92.58</t>
+          <t>-90.35</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>34077251.36886396</t>
+          <t>34060096.23319328</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>19073908.2</v>
+        <v>18335692.4</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>18155302.7</t>
+          <t>17372820.2</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>16618262.3</v>
+        <v>16470596.92</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>918605</t>
+          <t>962872</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>221276.1079384292</t>
+          <t>-11156.53313210487</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-570777.0106915683</t>
+          <t>-1289536.059020042</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>9666474.0</t>
+          <t>7072240.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CS10" t="inlineStr">
-        <is>
-          <t>103.5</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5281,42 +5281,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>93.449</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>126.465</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-8.41</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>82.54</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>101.08</v>
+        <v>101.26</v>
       </c>
       <c r="AZ11" t="n">
-        <v>101.11</v>
+        <v>101.09</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>104.05</t>
+          <t>104.08</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>247.67</t>
+          <t>146.84</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-92.58</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>34077251.36886396</t>
+          <t>34060096.23319328</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>20939130.4</v>
+        <v>19073908.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>18278584.3</t>
+          <t>18155302.7</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>16711913.28</v>
+        <v>16618262.3</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>2660546</t>
+          <t>918605</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>365285.7658711561</t>
+          <t>221276.1079384292</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>198452.8801595196</t>
+          <t>-570777.0106915683</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>13094151.0</t>
+          <t>9666474.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,14 +5716,14 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
       <c r="CR11" t="inlineStr">
         <is>
           <t>103.0</t>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>156.726</t>
+          <t>126.465</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,261 +5954,261 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>92.06</t>
+          <t>82.54</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>104.05</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>247.67</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>-95.31</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>34060096.23319328</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>20939130.4</v>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>18278584.3</t>
+        </is>
+      </c>
+      <c r="BL12" t="n">
+        <v>16711913.28</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>2660546</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>365285.7658711561</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>198452.8801595196</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>13094151.0</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>0.7848146795386409</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>-28.78483981056313</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>-7.753976956109076</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>32.64%</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>15.64%</t>
+        </is>
+      </c>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>40.56</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>程式控制86.38%、電子13.62% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>巨路-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="AY12" t="n">
-        <v>100.84</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>101.13</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>104.01</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>734.33</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>-98.21</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>34077251.36886396</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BJ12" t="n">
-        <v>22233266</v>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>17863358.6</t>
-        </is>
-      </c>
-      <c r="BL12" t="n">
-        <v>16748608.22</v>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>4369907</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>395619.0178187264</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>923014.0142268091</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>16160410.0</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>0.7848146795386409</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>-28.78483981056313</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>-7.753976956109076</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="CH12" t="inlineStr">
-        <is>
-          <t>9.42</t>
-        </is>
-      </c>
-      <c r="CI12" t="inlineStr">
-        <is>
-          <t>32.64%</t>
-        </is>
-      </c>
-      <c r="CJ12" t="inlineStr">
-        <is>
-          <t>15.64%</t>
-        </is>
-      </c>
-      <c r="CK12" t="inlineStr">
-        <is>
-          <t>40.95</t>
-        </is>
-      </c>
-      <c r="CL12" t="inlineStr">
-        <is>
-          <t>9952</t>
-        </is>
-      </c>
-      <c r="CM12" t="inlineStr">
-        <is>
-          <t>程式控制86.38%、電子13.62% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN12" t="inlineStr">
-        <is>
-          <t>巨路-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CO12" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CP12" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CQ12" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">

--- a/Result/checksun_type/設備維護.xlsx
+++ b/Result/checksun_type/設備維護.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>140.395</t>
+          <t>97.003</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1153,247 +1153,247 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>103.6</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>101.14</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>103.46</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>5.59</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>-82.43</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>34033584.98601399</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>10069703.0</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>14282531.4</v>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>13191597.5</t>
+        </is>
+      </c>
+      <c r="BL2" t="n">
+        <v>16233758.6</v>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>1090933</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-566690.6834109875</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-715121.363675382</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>10069703.0</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>102.64</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>103.54</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>3.71</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>-82.68</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>34060096.23319328</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>14552323.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>16568690.2</v>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>13151274.6</t>
-        </is>
-      </c>
-      <c r="BL2" t="n">
-        <v>16279672.76</v>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>3417415</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-539703.2869992794</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-382362.7727621086</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>14552323.0</t>
-        </is>
-      </c>
